--- a/research/traditional_assets/database/data/south_africa/south_africa_recreation.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="otcpk_leat" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.375</v>
+        <v>0.148</v>
+      </c>
+      <c r="E2">
+        <v>0.0163</v>
       </c>
       <c r="G2">
-        <v>0.2214446952595937</v>
+        <v>0.3434782608695652</v>
       </c>
       <c r="H2">
-        <v>0.198645598194131</v>
+        <v>0.2919254658385093</v>
       </c>
       <c r="I2">
-        <v>0.2245231096786542</v>
+        <v>0.0332874190308598</v>
       </c>
       <c r="J2">
-        <v>0.1685057277689294</v>
+        <v>0.0270890720389066</v>
       </c>
       <c r="K2">
-        <v>14.9</v>
+        <v>1.18</v>
       </c>
       <c r="L2">
-        <v>0.1681715575620768</v>
+        <v>0.02443064182194617</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,70 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.84</v>
+        <v>10.8</v>
       </c>
       <c r="V2">
-        <v>0.04372177055103884</v>
+        <v>0.1894736842105263</v>
       </c>
       <c r="W2">
-        <v>0.6182572614107884</v>
+        <v>0.02964824120603015</v>
       </c>
       <c r="X2">
-        <v>0.1498052101238164</v>
+        <v>0.120715049986476</v>
       </c>
       <c r="Y2">
-        <v>0.468452051286972</v>
+        <v>-0.09106680878044582</v>
       </c>
       <c r="Z2">
-        <v>3.884727522229918</v>
+        <v>1.330905251320704</v>
       </c>
       <c r="AA2">
-        <v>0.6545988383173421</v>
+        <v>0.03605298822998564</v>
       </c>
       <c r="AB2">
-        <v>0.1486925050013252</v>
+        <v>0.1195380782266475</v>
       </c>
       <c r="AC2">
-        <v>0.5059063333160169</v>
+        <v>-0.0834850899966619</v>
       </c>
       <c r="AD2">
-        <v>0.357</v>
+        <v>0.176</v>
       </c>
       <c r="AE2">
-        <v>1.151262412356184</v>
+        <v>0.9710883040473597</v>
       </c>
       <c r="AF2">
-        <v>1.508262412356184</v>
+        <v>1.14708830404736</v>
       </c>
       <c r="AG2">
-        <v>-3.331737587643816</v>
+        <v>-9.652911695952641</v>
       </c>
       <c r="AH2">
-        <v>0.01344163415358348</v>
+        <v>0.01972735587462796</v>
       </c>
       <c r="AI2">
-        <v>0.03651236639537351</v>
+        <v>0.02689722439828317</v>
       </c>
       <c r="AJ2">
-        <v>-0.03103093514588154</v>
+        <v>-0.2038755083304137</v>
       </c>
       <c r="AK2">
-        <v>-0.09135992140154602</v>
+        <v>-0.3031018598559253</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="AM2">
-        <v>-0.004</v>
+        <v>0.058</v>
       </c>
       <c r="AN2">
-        <v>0.01682137303868445</v>
+        <v>0.05982324949014276</v>
+      </c>
+      <c r="AO2">
+        <v>26.03448275862069</v>
       </c>
       <c r="AP2">
-        <v>-0.156987117167404</v>
+        <v>-3.281071276666431</v>
       </c>
       <c r="AQ2">
-        <v>-4950</v>
+        <v>26.03448275862069</v>
       </c>
     </row>
     <row r="3">
@@ -713,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.375</v>
+        <v>0.148</v>
+      </c>
+      <c r="E3">
+        <v>0.0163</v>
       </c>
       <c r="G3">
-        <v>0.2214446952595937</v>
+        <v>0.3434782608695652</v>
       </c>
       <c r="H3">
-        <v>0.198645598194131</v>
+        <v>0.2919254658385093</v>
       </c>
       <c r="I3">
-        <v>0.2245231096786542</v>
+        <v>0.0332874190308598</v>
       </c>
       <c r="J3">
-        <v>0.1685057277689294</v>
+        <v>0.0270890720389066</v>
       </c>
       <c r="K3">
-        <v>14.9</v>
+        <v>1.18</v>
       </c>
       <c r="L3">
-        <v>0.1681715575620768</v>
+        <v>0.02443064182194617</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,70 +766,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.84</v>
+        <v>10.8</v>
       </c>
       <c r="V3">
-        <v>0.04372177055103884</v>
+        <v>0.1894736842105263</v>
       </c>
       <c r="W3">
-        <v>0.6182572614107884</v>
+        <v>0.02964824120603015</v>
       </c>
       <c r="X3">
-        <v>0.1498052101238164</v>
+        <v>0.120715049986476</v>
       </c>
       <c r="Y3">
-        <v>0.468452051286972</v>
+        <v>-0.09106680878044582</v>
       </c>
       <c r="Z3">
-        <v>3.884727522229918</v>
+        <v>1.330905251320704</v>
       </c>
       <c r="AA3">
-        <v>0.6545988383173421</v>
+        <v>0.03605298822998564</v>
       </c>
       <c r="AB3">
-        <v>0.1486925050013252</v>
+        <v>0.1195380782266475</v>
       </c>
       <c r="AC3">
-        <v>0.5059063333160169</v>
+        <v>-0.0834850899966619</v>
       </c>
       <c r="AD3">
-        <v>0.357</v>
+        <v>0.176</v>
       </c>
       <c r="AE3">
-        <v>1.151262412356184</v>
+        <v>0.9710883040473597</v>
       </c>
       <c r="AF3">
-        <v>1.508262412356184</v>
+        <v>1.14708830404736</v>
       </c>
       <c r="AG3">
-        <v>-3.331737587643816</v>
+        <v>-9.652911695952641</v>
       </c>
       <c r="AH3">
-        <v>0.01344163415358348</v>
+        <v>0.01972735587462796</v>
       </c>
       <c r="AI3">
-        <v>0.03651236639537351</v>
+        <v>0.02689722439828317</v>
       </c>
       <c r="AJ3">
-        <v>-0.03103093514588154</v>
+        <v>-0.2038755083304137</v>
       </c>
       <c r="AK3">
-        <v>-0.09135992140154602</v>
+        <v>-0.3031018598559253</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="AM3">
-        <v>-0.004</v>
+        <v>0.058</v>
       </c>
       <c r="AN3">
-        <v>0.01682137303868445</v>
+        <v>0.05982324949014276</v>
+      </c>
+      <c r="AO3">
+        <v>26.03448275862069</v>
       </c>
       <c r="AP3">
-        <v>-0.156987117167404</v>
+        <v>-3.281071276666431</v>
       </c>
       <c r="AQ3">
-        <v>-4950</v>
+        <v>26.03448275862069</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Leatt Corporation (OTCPK:LEAT)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OTCPK:LEAT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>31.0689655172414</v>
+      </c>
+      <c r="F2">
+        <v>4.68344775077994</v>
+      </c>
+      <c r="G2">
+        <v>0.389900851137784</v>
+      </c>
+      <c r="H2">
+        <v>2.56938187611358</v>
+      </c>
+      <c r="I2">
+        <v>0.019727355874628</v>
+      </c>
+      <c r="J2">
+        <v>0.13</v>
+      </c>
+      <c r="K2">
+        <v>57</v>
+      </c>
+      <c r="L2">
+        <v>52.4507086415882</v>
+      </c>
+      <c r="M2">
+        <v>47.3470883040474</v>
+      </c>
+      <c r="N2">
+        <v>49.2098301211143</v>
+      </c>
+      <c r="O2">
+        <v>1.14708830404736</v>
+      </c>
+      <c r="P2">
+        <v>7.55912147952616</v>
+      </c>
+      <c r="Q2">
+        <v>0.119538078226648</v>
+      </c>
+      <c r="R2">
+        <v>0.116481896277386</v>
+      </c>
+      <c r="S2">
+        <v>0.0610531385114472</v>
+      </c>
+      <c r="T2">
+        <v>0.037157</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.120715049986476</v>
+      </c>
+      <c r="X2">
+        <v>0.128335041698144</v>
+      </c>
+      <c r="Y2">
+        <v>0.910122596249745</v>
+      </c>
+      <c r="Z2">
+        <v>0.99478501959161</v>
+      </c>
+      <c r="AA2">
+        <v>0.1759999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.083634436317051</v>
+      </c>
+      <c r="AC2">
+        <v>31.06896551724137</v>
+      </c>
+      <c r="AD2">
+        <v>1.14708830404736</v>
+      </c>
+      <c r="AE2">
+        <v>0.058</v>
+      </c>
+      <c r="AF2">
+        <v>1.14</v>
+      </c>
+      <c r="AG2">
+        <v>2.942</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>57</v>
+      </c>
+      <c r="AK2">
+        <v>0.0900044129483385</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.27</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.69</v>
+      </c>
+      <c r="AR2">
+        <v>0.058</v>
+      </c>
+      <c r="AS2">
+        <v>0.1759999999999999</v>
+      </c>
+      <c r="AT2">
+        <v>10.8</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1195290768757234</v>
+      </c>
+      <c r="C2">
+        <v>58.15236753890989</v>
+      </c>
+      <c r="D2">
+        <v>47.35236753890989</v>
+      </c>
+      <c r="E2">
+        <v>-1.14708830404736</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>10.8</v>
+      </c>
+      <c r="H2">
+        <v>57</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.942</v>
+      </c>
+      <c r="K2">
+        <v>1.14</v>
+      </c>
+      <c r="L2">
+        <v>1.802</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.802</v>
+      </c>
+      <c r="O2">
+        <v>0.48654</v>
+      </c>
+      <c r="P2">
+        <v>1.31546</v>
+      </c>
+      <c r="Q2">
+        <v>2.45546</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1195290768757234</v>
+      </c>
+      <c r="T2">
+        <v>0.8969457633378592</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.27</v>
+      </c>
+      <c r="W2">
+        <v>0.032631</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1192494183681589</v>
+      </c>
+      <c r="C3">
+        <v>57.73550309683799</v>
+      </c>
+      <c r="D3">
+        <v>47.51697397987846</v>
+      </c>
+      <c r="E3">
+        <v>-0.5656174210068861</v>
+      </c>
+      <c r="F3">
+        <v>0.5814708830404736</v>
+      </c>
+      <c r="G3">
+        <v>10.8</v>
+      </c>
+      <c r="H3">
+        <v>57</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.942</v>
+      </c>
+      <c r="K3">
+        <v>1.14</v>
+      </c>
+      <c r="L3">
+        <v>1.802</v>
+      </c>
+      <c r="M3">
+        <v>0.02599174847190917</v>
+      </c>
+      <c r="N3">
+        <v>1.776008251528091</v>
+      </c>
+      <c r="O3">
+        <v>0.4795222279125845</v>
+      </c>
+      <c r="P3">
+        <v>1.296486023615506</v>
+      </c>
+      <c r="Q3">
+        <v>2.436486023615506</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1201243518870292</v>
+      </c>
+      <c r="T3">
+        <v>0.9035596058351991</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.27</v>
+      </c>
+      <c r="W3">
+        <v>0.032631</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>69.32969522798855</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1189697598605945</v>
+      </c>
+      <c r="C4">
+        <v>57.3197870576476</v>
+      </c>
+      <c r="D4">
+        <v>47.68272882372855</v>
+      </c>
+      <c r="E4">
+        <v>0.01585346203358751</v>
+      </c>
+      <c r="F4">
+        <v>1.162941766080947</v>
+      </c>
+      <c r="G4">
+        <v>10.8</v>
+      </c>
+      <c r="H4">
+        <v>57</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.942</v>
+      </c>
+      <c r="K4">
+        <v>1.14</v>
+      </c>
+      <c r="L4">
+        <v>1.802</v>
+      </c>
+      <c r="M4">
+        <v>0.05198349694381834</v>
+      </c>
+      <c r="N4">
+        <v>1.750016503056181</v>
+      </c>
+      <c r="O4">
+        <v>0.472504455825169</v>
+      </c>
+      <c r="P4">
+        <v>1.277512047231012</v>
+      </c>
+      <c r="Q4">
+        <v>2.417512047231012</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1207317753679535</v>
+      </c>
+      <c r="T4">
+        <v>0.9103084247100356</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.27</v>
+      </c>
+      <c r="W4">
+        <v>0.032631</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>34.66484761399428</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.11869010135303</v>
+      </c>
+      <c r="C5">
+        <v>56.90523148142993</v>
+      </c>
+      <c r="D5">
+        <v>47.84964413055135</v>
+      </c>
+      <c r="E5">
+        <v>0.5973243450740611</v>
+      </c>
+      <c r="F5">
+        <v>1.744412649121421</v>
+      </c>
+      <c r="G5">
+        <v>10.8</v>
+      </c>
+      <c r="H5">
+        <v>57</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.942</v>
+      </c>
+      <c r="K5">
+        <v>1.14</v>
+      </c>
+      <c r="L5">
+        <v>1.802</v>
+      </c>
+      <c r="M5">
+        <v>0.07797524541572751</v>
+      </c>
+      <c r="N5">
+        <v>1.724024754584272</v>
+      </c>
+      <c r="O5">
+        <v>0.4654866837377536</v>
+      </c>
+      <c r="P5">
+        <v>1.258538070846519</v>
+      </c>
+      <c r="Q5">
+        <v>2.398538070846519</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1213517230443608</v>
+      </c>
+      <c r="T5">
+        <v>0.9171963944895078</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.27</v>
+      </c>
+      <c r="W5">
+        <v>0.032631</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>23.10989840932952</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1184104428454656</v>
+      </c>
+      <c r="C6">
+        <v>56.49184859773665</v>
+      </c>
+      <c r="D6">
+        <v>48.01773212989855</v>
+      </c>
+      <c r="E6">
+        <v>1.178795228114535</v>
+      </c>
+      <c r="F6">
+        <v>2.325883532161894</v>
+      </c>
+      <c r="G6">
+        <v>10.8</v>
+      </c>
+      <c r="H6">
+        <v>57</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.942</v>
+      </c>
+      <c r="K6">
+        <v>1.14</v>
+      </c>
+      <c r="L6">
+        <v>1.802</v>
+      </c>
+      <c r="M6">
+        <v>0.1039669938876367</v>
+      </c>
+      <c r="N6">
+        <v>1.698033006112363</v>
+      </c>
+      <c r="O6">
+        <v>0.4584689116503381</v>
+      </c>
+      <c r="P6">
+        <v>1.239564094462025</v>
+      </c>
+      <c r="Q6">
+        <v>2.379564094462025</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.12198458629736</v>
+      </c>
+      <c r="T6">
+        <v>0.9242278636393859</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.27</v>
+      </c>
+      <c r="W6">
+        <v>0.032631</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>17.33242380699714</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1181307843379011</v>
+      </c>
+      <c r="C7">
+        <v>56.07965080856703</v>
+      </c>
+      <c r="D7">
+        <v>48.1870052237694</v>
+      </c>
+      <c r="E7">
+        <v>1.760266111155009</v>
+      </c>
+      <c r="F7">
+        <v>2.907354415202368</v>
+      </c>
+      <c r="G7">
+        <v>10.8</v>
+      </c>
+      <c r="H7">
+        <v>57</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.942</v>
+      </c>
+      <c r="K7">
+        <v>1.14</v>
+      </c>
+      <c r="L7">
+        <v>1.802</v>
+      </c>
+      <c r="M7">
+        <v>0.1299587423595459</v>
+      </c>
+      <c r="N7">
+        <v>1.672041257640454</v>
+      </c>
+      <c r="O7">
+        <v>0.4514511395629226</v>
+      </c>
+      <c r="P7">
+        <v>1.220590118077531</v>
+      </c>
+      <c r="Q7">
+        <v>2.360590118077531</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1226307729872643</v>
+      </c>
+      <c r="T7">
+        <v>0.9314073637187349</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.27</v>
+      </c>
+      <c r="W7">
+        <v>0.032631</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>13.86593904559771</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1178993058303367</v>
+      </c>
+      <c r="C8">
+        <v>55.63919577814509</v>
+      </c>
+      <c r="D8">
+        <v>48.32802107638793</v>
+      </c>
+      <c r="E8">
+        <v>2.341736994195482</v>
+      </c>
+      <c r="F8">
+        <v>3.488825298242841</v>
+      </c>
+      <c r="G8">
+        <v>10.8</v>
+      </c>
+      <c r="H8">
+        <v>57</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.942</v>
+      </c>
+      <c r="K8">
+        <v>1.14</v>
+      </c>
+      <c r="L8">
+        <v>1.802</v>
+      </c>
+      <c r="M8">
+        <v>0.1597881986595221</v>
+      </c>
+      <c r="N8">
+        <v>1.642211801340478</v>
+      </c>
+      <c r="O8">
+        <v>0.443397186361929</v>
+      </c>
+      <c r="P8">
+        <v>1.198814614978549</v>
+      </c>
+      <c r="Q8">
+        <v>2.338814614978548</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1232907083301454</v>
+      </c>
+      <c r="T8">
+        <v>0.9387396191189212</v>
+      </c>
+      <c r="U8">
+        <v>0.0458</v>
+      </c>
+      <c r="V8">
+        <v>0.27</v>
+      </c>
+      <c r="W8">
+        <v>0.033434</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>11.27742859057892</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1177400973227722</v>
+      </c>
+      <c r="C9">
+        <v>55.15519414546106</v>
+      </c>
+      <c r="D9">
+        <v>48.42549032674437</v>
+      </c>
+      <c r="E9">
+        <v>2.923207877235956</v>
+      </c>
+      <c r="F9">
+        <v>4.070296181283315</v>
+      </c>
+      <c r="G9">
+        <v>10.8</v>
+      </c>
+      <c r="H9">
+        <v>57</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.942</v>
+      </c>
+      <c r="K9">
+        <v>1.14</v>
+      </c>
+      <c r="L9">
+        <v>1.802</v>
+      </c>
+      <c r="M9">
+        <v>0.1953742167015991</v>
+      </c>
+      <c r="N9">
+        <v>1.606625783298401</v>
+      </c>
+      <c r="O9">
+        <v>0.4337889614905682</v>
+      </c>
+      <c r="P9">
+        <v>1.172836821807833</v>
+      </c>
+      <c r="Q9">
+        <v>2.312836821807832</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1239648358309379</v>
+      </c>
+      <c r="T9">
+        <v>0.9462295574309395</v>
+      </c>
+      <c r="U9">
+        <v>0.048</v>
+      </c>
+      <c r="V9">
+        <v>0.27</v>
+      </c>
+      <c r="W9">
+        <v>0.03504</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>9.223325525866334</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1174845288152078</v>
+      </c>
+      <c r="C10">
+        <v>54.73100996766281</v>
+      </c>
+      <c r="D10">
+        <v>48.58277703198661</v>
+      </c>
+      <c r="E10">
+        <v>3.504678760276429</v>
+      </c>
+      <c r="F10">
+        <v>4.651767064323789</v>
+      </c>
+      <c r="G10">
+        <v>10.8</v>
+      </c>
+      <c r="H10">
+        <v>57</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.942</v>
+      </c>
+      <c r="K10">
+        <v>1.14</v>
+      </c>
+      <c r="L10">
+        <v>1.802</v>
+      </c>
+      <c r="M10">
+        <v>0.2232848190875419</v>
+      </c>
+      <c r="N10">
+        <v>1.578715180912458</v>
+      </c>
+      <c r="O10">
+        <v>0.4262530988463637</v>
+      </c>
+      <c r="P10">
+        <v>1.152462082066094</v>
+      </c>
+      <c r="Q10">
+        <v>2.292462082066094</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1246536182773997</v>
+      </c>
+      <c r="T10">
+        <v>0.9538823204888712</v>
+      </c>
+      <c r="U10">
+        <v>0.048</v>
+      </c>
+      <c r="V10">
+        <v>0.27</v>
+      </c>
+      <c r="W10">
+        <v>0.03504</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>8.070409835133042</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1173275103076433</v>
+      </c>
+      <c r="C11">
+        <v>54.24668204908174</v>
+      </c>
+      <c r="D11">
+        <v>48.679919996446</v>
+      </c>
+      <c r="E11">
+        <v>4.086149643316902</v>
+      </c>
+      <c r="F11">
+        <v>5.233237947364262</v>
+      </c>
+      <c r="G11">
+        <v>10.8</v>
+      </c>
+      <c r="H11">
+        <v>57</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.942</v>
+      </c>
+      <c r="K11">
+        <v>1.14</v>
+      </c>
+      <c r="L11">
+        <v>1.802</v>
+      </c>
+      <c r="M11">
+        <v>0.259045278394531</v>
+      </c>
+      <c r="N11">
+        <v>1.542954721605469</v>
+      </c>
+      <c r="O11">
+        <v>0.4165977748334766</v>
+      </c>
+      <c r="P11">
+        <v>1.126356946771992</v>
+      </c>
+      <c r="Q11">
+        <v>2.266356946771992</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.125357538799608</v>
+      </c>
+      <c r="T11">
+        <v>0.9617032761414828</v>
+      </c>
+      <c r="U11">
+        <v>0.0495</v>
+      </c>
+      <c r="V11">
+        <v>0.27</v>
+      </c>
+      <c r="W11">
+        <v>0.036135</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>6.956312854525451</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1170828918000788</v>
+      </c>
+      <c r="C12">
+        <v>53.81732625918701</v>
+      </c>
+      <c r="D12">
+        <v>48.83203508959176</v>
+      </c>
+      <c r="E12">
+        <v>4.667620526357377</v>
+      </c>
+      <c r="F12">
+        <v>5.814708830404737</v>
+      </c>
+      <c r="G12">
+        <v>10.8</v>
+      </c>
+      <c r="H12">
+        <v>57</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.942</v>
+      </c>
+      <c r="K12">
+        <v>1.14</v>
+      </c>
+      <c r="L12">
+        <v>1.802</v>
+      </c>
+      <c r="M12">
+        <v>0.2878280871050345</v>
+      </c>
+      <c r="N12">
+        <v>1.514171912894965</v>
+      </c>
+      <c r="O12">
+        <v>0.4088264164816406</v>
+      </c>
+      <c r="P12">
+        <v>1.105345496413325</v>
+      </c>
+      <c r="Q12">
+        <v>2.245345496413325</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1260771020000876</v>
+      </c>
+      <c r="T12">
+        <v>0.9696980308085967</v>
+      </c>
+      <c r="U12">
+        <v>0.0495</v>
+      </c>
+      <c r="V12">
+        <v>0.27</v>
+      </c>
+      <c r="W12">
+        <v>0.036135</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>6.260681569072904</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1169506932925144</v>
+      </c>
+      <c r="C13">
+        <v>53.31845889363572</v>
+      </c>
+      <c r="D13">
+        <v>48.91463860708092</v>
+      </c>
+      <c r="E13">
+        <v>5.24909140939785</v>
+      </c>
+      <c r="F13">
+        <v>6.39617971344521</v>
+      </c>
+      <c r="G13">
+        <v>10.8</v>
+      </c>
+      <c r="H13">
+        <v>57</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.942</v>
+      </c>
+      <c r="K13">
+        <v>1.14</v>
+      </c>
+      <c r="L13">
+        <v>1.802</v>
+      </c>
+      <c r="M13">
+        <v>0.3255655474143612</v>
+      </c>
+      <c r="N13">
+        <v>1.476434452585639</v>
+      </c>
+      <c r="O13">
+        <v>0.3986373021981224</v>
+      </c>
+      <c r="P13">
+        <v>1.077797150387516</v>
+      </c>
+      <c r="Q13">
+        <v>2.217797150387516</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1268128351601285</v>
+      </c>
+      <c r="T13">
+        <v>0.9778724428839605</v>
+      </c>
+      <c r="U13">
+        <v>0.0509</v>
+      </c>
+      <c r="V13">
+        <v>0.27</v>
+      </c>
+      <c r="W13">
+        <v>0.037157</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>5.534983705467205</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.11671629478495</v>
+      </c>
+      <c r="C14">
+        <v>52.88413974976864</v>
+      </c>
+      <c r="D14">
+        <v>49.06179034625433</v>
+      </c>
+      <c r="E14">
+        <v>5.830562292438323</v>
+      </c>
+      <c r="F14">
+        <v>6.977650596485683</v>
+      </c>
+      <c r="G14">
+        <v>10.8</v>
+      </c>
+      <c r="H14">
+        <v>57</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.942</v>
+      </c>
+      <c r="K14">
+        <v>1.14</v>
+      </c>
+      <c r="L14">
+        <v>1.802</v>
+      </c>
+      <c r="M14">
+        <v>0.3551624153611213</v>
+      </c>
+      <c r="N14">
+        <v>1.446837584638879</v>
+      </c>
+      <c r="O14">
+        <v>0.3906461478524972</v>
+      </c>
+      <c r="P14">
+        <v>1.056191436786381</v>
+      </c>
+      <c r="Q14">
+        <v>2.196191436786381</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1275652895283522</v>
+      </c>
+      <c r="T14">
+        <v>0.9862326370519462</v>
+      </c>
+      <c r="U14">
+        <v>0.0509</v>
+      </c>
+      <c r="V14">
+        <v>0.27</v>
+      </c>
+      <c r="W14">
+        <v>0.037157</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.073735063344938</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1164818962773855</v>
+      </c>
+      <c r="C15">
+        <v>52.45070864158818</v>
+      </c>
+      <c r="D15">
+        <v>49.20983012111434</v>
+      </c>
+      <c r="E15">
+        <v>6.412033175478797</v>
+      </c>
+      <c r="F15">
+        <v>7.559121479526157</v>
+      </c>
+      <c r="G15">
+        <v>10.8</v>
+      </c>
+      <c r="H15">
+        <v>57</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.942</v>
+      </c>
+      <c r="K15">
+        <v>1.14</v>
+      </c>
+      <c r="L15">
+        <v>1.802</v>
+      </c>
+      <c r="M15">
+        <v>0.3847592833078814</v>
+      </c>
+      <c r="N15">
+        <v>1.417240716692118</v>
+      </c>
+      <c r="O15">
+        <v>0.382654993506872</v>
+      </c>
+      <c r="P15">
+        <v>1.034585723185246</v>
+      </c>
+      <c r="Q15">
+        <v>2.174585723185246</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1283350416981442</v>
+      </c>
+      <c r="T15">
+        <v>0.9947850195916096</v>
+      </c>
+      <c r="U15">
+        <v>0.0509</v>
+      </c>
+      <c r="V15">
+        <v>0.27</v>
+      </c>
+      <c r="W15">
+        <v>0.037157</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>4.683447750779942</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.116513217769821</v>
+      </c>
+      <c r="C16">
+        <v>51.84940425575211</v>
+      </c>
+      <c r="D16">
+        <v>49.18999661831874</v>
+      </c>
+      <c r="E16">
+        <v>6.993504058519271</v>
+      </c>
+      <c r="F16">
+        <v>8.140592362566631</v>
+      </c>
+      <c r="G16">
+        <v>10.8</v>
+      </c>
+      <c r="H16">
+        <v>57</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.942</v>
+      </c>
+      <c r="K16">
+        <v>1.14</v>
+      </c>
+      <c r="L16">
+        <v>1.802</v>
+      </c>
+      <c r="M16">
+        <v>0.4355216913973147</v>
+      </c>
+      <c r="N16">
+        <v>1.366478308602685</v>
+      </c>
+      <c r="O16">
+        <v>0.368949143322725</v>
+      </c>
+      <c r="P16">
+        <v>0.9975291652799601</v>
+      </c>
+      <c r="Q16">
+        <v>2.13752916527996</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1291226950811872</v>
+      </c>
+      <c r="T16">
+        <v>1.003536294748474</v>
+      </c>
+      <c r="U16">
+        <v>0.0535</v>
+      </c>
+      <c r="V16">
+        <v>0.27</v>
+      </c>
+      <c r="W16">
+        <v>0.039055</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>4.137566591042841</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1165934492622566</v>
+      </c>
+      <c r="C17">
+        <v>51.21720176382921</v>
+      </c>
+      <c r="D17">
+        <v>49.13926500943631</v>
+      </c>
+      <c r="E17">
+        <v>7.574974941559743</v>
+      </c>
+      <c r="F17">
+        <v>8.722063245607103</v>
+      </c>
+      <c r="G17">
+        <v>10.8</v>
+      </c>
+      <c r="H17">
+        <v>57</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.942</v>
+      </c>
+      <c r="K17">
+        <v>1.14</v>
+      </c>
+      <c r="L17">
+        <v>1.802</v>
+      </c>
+      <c r="M17">
+        <v>0.4901799544031192</v>
+      </c>
+      <c r="N17">
+        <v>1.311820045596881</v>
+      </c>
+      <c r="O17">
+        <v>0.3541914123111578</v>
+      </c>
+      <c r="P17">
+        <v>0.9576286332857229</v>
+      </c>
+      <c r="Q17">
+        <v>2.097628633285723</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1299288814850078</v>
+      </c>
+      <c r="T17">
+        <v>1.012493482261972</v>
+      </c>
+      <c r="U17">
+        <v>0.0562</v>
+      </c>
+      <c r="V17">
+        <v>0.27</v>
+      </c>
+      <c r="W17">
+        <v>0.041026</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>3.676200921341742</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1169467007546921</v>
+      </c>
+      <c r="C18">
+        <v>50.41360354164159</v>
+      </c>
+      <c r="D18">
+        <v>48.91713767028916</v>
+      </c>
+      <c r="E18">
+        <v>8.156445824600217</v>
+      </c>
+      <c r="F18">
+        <v>9.303534128647577</v>
+      </c>
+      <c r="G18">
+        <v>10.8</v>
+      </c>
+      <c r="H18">
+        <v>57</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.942</v>
+      </c>
+      <c r="K18">
+        <v>1.14</v>
+      </c>
+      <c r="L18">
+        <v>1.802</v>
+      </c>
+      <c r="M18">
+        <v>0.5665852284346374</v>
+      </c>
+      <c r="N18">
+        <v>1.235414771565362</v>
+      </c>
+      <c r="O18">
+        <v>0.3335619883226478</v>
+      </c>
+      <c r="P18">
+        <v>0.9018527832427145</v>
+      </c>
+      <c r="Q18">
+        <v>2.041852783242714</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1307542628032049</v>
+      </c>
+      <c r="T18">
+        <v>1.021663936144838</v>
+      </c>
+      <c r="U18">
+        <v>0.0609</v>
+      </c>
+      <c r="V18">
+        <v>0.27</v>
+      </c>
+      <c r="W18">
+        <v>0.044457</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>3.180457077884943</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1179394322471277</v>
+      </c>
+      <c r="C19">
+        <v>49.21851209415912</v>
+      </c>
+      <c r="D19">
+        <v>48.30351710584717</v>
+      </c>
+      <c r="E19">
+        <v>8.737916707640691</v>
+      </c>
+      <c r="F19">
+        <v>9.885005011688051</v>
+      </c>
+      <c r="G19">
+        <v>10.8</v>
+      </c>
+      <c r="H19">
+        <v>57</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.942</v>
+      </c>
+      <c r="K19">
+        <v>1.14</v>
+      </c>
+      <c r="L19">
+        <v>1.802</v>
+      </c>
+      <c r="M19">
+        <v>0.6939273518205011</v>
+      </c>
+      <c r="N19">
+        <v>1.108072648179499</v>
+      </c>
+      <c r="O19">
+        <v>0.2991796150084647</v>
+      </c>
+      <c r="P19">
+        <v>0.808893033171034</v>
+      </c>
+      <c r="Q19">
+        <v>1.948893033171034</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1315995328278647</v>
+      </c>
+      <c r="T19">
+        <v>1.031055364820062</v>
+      </c>
+      <c r="U19">
+        <v>0.0702</v>
+      </c>
+      <c r="V19">
+        <v>0.27</v>
+      </c>
+      <c r="W19">
+        <v>0.051246</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>2.596813622164478</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1184635037395632</v>
+      </c>
+      <c r="C20">
+        <v>48.31927341142073</v>
+      </c>
+      <c r="D20">
+        <v>47.98574930614926</v>
+      </c>
+      <c r="E20">
+        <v>9.319387590681163</v>
+      </c>
+      <c r="F20">
+        <v>10.46647589472852</v>
+      </c>
+      <c r="G20">
+        <v>10.8</v>
+      </c>
+      <c r="H20">
+        <v>57</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.942</v>
+      </c>
+      <c r="K20">
+        <v>1.14</v>
+      </c>
+      <c r="L20">
+        <v>1.802</v>
+      </c>
+      <c r="M20">
+        <v>0.7839390445151664</v>
+      </c>
+      <c r="N20">
+        <v>1.018060955484833</v>
+      </c>
+      <c r="O20">
+        <v>0.274876457980905</v>
+      </c>
+      <c r="P20">
+        <v>0.7431844975039283</v>
+      </c>
+      <c r="Q20">
+        <v>1.883184497503928</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1324654191945893</v>
+      </c>
+      <c r="T20">
+        <v>1.040675852731267</v>
+      </c>
+      <c r="U20">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V20">
+        <v>0.27</v>
+      </c>
+      <c r="W20">
+        <v>0.054677</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>2.298648106134912</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1184043052319988</v>
+      </c>
+      <c r="C21">
+        <v>47.77348759258636</v>
+      </c>
+      <c r="D21">
+        <v>48.02143437035536</v>
+      </c>
+      <c r="E21">
+        <v>9.900858473721639</v>
+      </c>
+      <c r="F21">
+        <v>11.047946777769</v>
+      </c>
+      <c r="G21">
+        <v>10.8</v>
+      </c>
+      <c r="H21">
+        <v>57</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.942</v>
+      </c>
+      <c r="K21">
+        <v>1.14</v>
+      </c>
+      <c r="L21">
+        <v>1.802</v>
+      </c>
+      <c r="M21">
+        <v>0.827491213654898</v>
+      </c>
+      <c r="N21">
+        <v>0.9745087863451019</v>
+      </c>
+      <c r="O21">
+        <v>0.2631173723131775</v>
+      </c>
+      <c r="P21">
+        <v>0.7113914140319244</v>
+      </c>
+      <c r="Q21">
+        <v>1.851391414031924</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1333526854716034</v>
+      </c>
+      <c r="T21">
+        <v>1.050533883553861</v>
+      </c>
+      <c r="U21">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V21">
+        <v>0.27</v>
+      </c>
+      <c r="W21">
+        <v>0.054677</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.177666626864653</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1183451067244343</v>
+      </c>
+      <c r="C22">
+        <v>47.2277548883339</v>
+      </c>
+      <c r="D22">
+        <v>48.05717254914337</v>
+      </c>
+      <c r="E22">
+        <v>10.48232935676211</v>
+      </c>
+      <c r="F22">
+        <v>11.62941766080947</v>
+      </c>
+      <c r="G22">
+        <v>10.8</v>
+      </c>
+      <c r="H22">
+        <v>57</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.942</v>
+      </c>
+      <c r="K22">
+        <v>1.14</v>
+      </c>
+      <c r="L22">
+        <v>1.802</v>
+      </c>
+      <c r="M22">
+        <v>0.8710433827946295</v>
+      </c>
+      <c r="N22">
+        <v>0.9309566172053704</v>
+      </c>
+      <c r="O22">
+        <v>0.25135828664545</v>
+      </c>
+      <c r="P22">
+        <v>0.6795983305599204</v>
+      </c>
+      <c r="Q22">
+        <v>1.81959833055992</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1342621334055429</v>
+      </c>
+      <c r="T22">
+        <v>1.060638365147019</v>
+      </c>
+      <c r="U22">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V22">
+        <v>0.27</v>
+      </c>
+      <c r="W22">
+        <v>0.054677</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.06878329552142</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1207846982168699</v>
+      </c>
+      <c r="C23">
+        <v>45.21626264946347</v>
+      </c>
+      <c r="D23">
+        <v>46.62715119331342</v>
+      </c>
+      <c r="E23">
+        <v>11.06380023980259</v>
+      </c>
+      <c r="F23">
+        <v>12.21088854384995</v>
+      </c>
+      <c r="G23">
+        <v>10.8</v>
+      </c>
+      <c r="H23">
+        <v>57</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.942</v>
+      </c>
+      <c r="K23">
+        <v>1.14</v>
+      </c>
+      <c r="L23">
+        <v>1.802</v>
+      </c>
+      <c r="M23">
+        <v>1.113633035199115</v>
+      </c>
+      <c r="N23">
+        <v>0.6883669648008848</v>
+      </c>
+      <c r="O23">
+        <v>0.1858590804962389</v>
+      </c>
+      <c r="P23">
+        <v>0.5025078843046459</v>
+      </c>
+      <c r="Q23">
+        <v>1.642507884304646</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.13519460533781</v>
+      </c>
+      <c r="T23">
+        <v>1.070998656400763</v>
+      </c>
+      <c r="U23">
+        <v>0.0912</v>
+      </c>
+      <c r="V23">
+        <v>0.27</v>
+      </c>
+      <c r="W23">
+        <v>0.066576</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>1.618127285239708</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1208444897093054</v>
+      </c>
+      <c r="C24">
+        <v>44.6008113374174</v>
+      </c>
+      <c r="D24">
+        <v>46.59317076430783</v>
+      </c>
+      <c r="E24">
+        <v>11.64527112284306</v>
+      </c>
+      <c r="F24">
+        <v>12.79235942689042</v>
+      </c>
+      <c r="G24">
+        <v>10.8</v>
+      </c>
+      <c r="H24">
+        <v>57</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.942</v>
+      </c>
+      <c r="K24">
+        <v>1.14</v>
+      </c>
+      <c r="L24">
+        <v>1.802</v>
+      </c>
+      <c r="M24">
+        <v>1.166663179732406</v>
+      </c>
+      <c r="N24">
+        <v>0.6353368202675935</v>
+      </c>
+      <c r="O24">
+        <v>0.1715409414722503</v>
+      </c>
+      <c r="P24">
+        <v>0.4637958787953432</v>
+      </c>
+      <c r="Q24">
+        <v>1.603795878795343</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1361509868068018</v>
+      </c>
+      <c r="T24">
+        <v>1.081624596148193</v>
+      </c>
+      <c r="U24">
+        <v>0.0912</v>
+      </c>
+      <c r="V24">
+        <v>0.27</v>
+      </c>
+      <c r="W24">
+        <v>0.066576</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>1.544576045001539</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1339421858444569</v>
+      </c>
+      <c r="C25">
+        <v>37.6051174971515</v>
+      </c>
+      <c r="D25">
+        <v>40.17894780708239</v>
+      </c>
+      <c r="E25">
+        <v>12.22674200588353</v>
+      </c>
+      <c r="F25">
+        <v>13.37383030993089</v>
+      </c>
+      <c r="G25">
+        <v>10.8</v>
+      </c>
+      <c r="H25">
+        <v>57</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.942</v>
+      </c>
+      <c r="K25">
+        <v>1.14</v>
+      </c>
+      <c r="L25">
+        <v>1.802</v>
+      </c>
+      <c r="M25">
+        <v>2.094341826535178</v>
+      </c>
+      <c r="N25">
+        <v>-0.2923418265351783</v>
+      </c>
+      <c r="O25">
+        <v>-0.07893229316449814</v>
+      </c>
+      <c r="P25">
+        <v>-0.2134095333706801</v>
+      </c>
+      <c r="Q25">
+        <v>0.9265904666293198</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1380410217682114</v>
+      </c>
+      <c r="T25">
+        <v>1.102623954951793</v>
+      </c>
+      <c r="U25">
+        <v>0.1566</v>
+      </c>
+      <c r="V25">
+        <v>0.2323116474281175</v>
+      </c>
+      <c r="W25">
+        <v>0.1202199960127568</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.8604135089930278</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1351201858444568</v>
+      </c>
+      <c r="C26">
+        <v>36.53225636084495</v>
+      </c>
+      <c r="D26">
+        <v>39.68755755381632</v>
+      </c>
+      <c r="E26">
+        <v>12.80821288892401</v>
+      </c>
+      <c r="F26">
+        <v>13.95530119297137</v>
+      </c>
+      <c r="G26">
+        <v>10.8</v>
+      </c>
+      <c r="H26">
+        <v>57</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.942</v>
+      </c>
+      <c r="K26">
+        <v>1.14</v>
+      </c>
+      <c r="L26">
+        <v>1.802</v>
+      </c>
+      <c r="M26">
+        <v>2.185400166819316</v>
+      </c>
+      <c r="N26">
+        <v>-0.3834001668193163</v>
+      </c>
+      <c r="O26">
+        <v>-0.1035180450412154</v>
+      </c>
+      <c r="P26">
+        <v>-0.2798821217781009</v>
+      </c>
+      <c r="Q26">
+        <v>0.860117878221899</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1393468246862142</v>
+      </c>
+      <c r="T26">
+        <v>1.11713216488537</v>
+      </c>
+      <c r="U26">
+        <v>0.1566</v>
+      </c>
+      <c r="V26">
+        <v>0.222631995451946</v>
+      </c>
+      <c r="W26">
+        <v>0.1217358295122253</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.8245629461183184</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.150426558373007</v>
+      </c>
+      <c r="C27">
+        <v>30.50877822145711</v>
+      </c>
+      <c r="D27">
+        <v>34.24555029746895</v>
+      </c>
+      <c r="E27">
+        <v>13.38968377196448</v>
+      </c>
+      <c r="F27">
+        <v>14.53677207601184</v>
+      </c>
+      <c r="G27">
+        <v>10.8</v>
+      </c>
+      <c r="H27">
+        <v>57</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.942</v>
+      </c>
+      <c r="K27">
+        <v>1.14</v>
+      </c>
+      <c r="L27">
+        <v>1.802</v>
+      </c>
+      <c r="M27">
+        <v>3.035278009471272</v>
+      </c>
+      <c r="N27">
+        <v>-1.233278009471272</v>
+      </c>
+      <c r="O27">
+        <v>-0.3329850625572435</v>
+      </c>
+      <c r="P27">
+        <v>-0.9002929469140288</v>
+      </c>
+      <c r="Q27">
+        <v>0.2397070530859711</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1421252790534306</v>
+      </c>
+      <c r="T27">
+        <v>1.148002366425501</v>
+      </c>
+      <c r="U27">
+        <v>0.2088</v>
+      </c>
+      <c r="V27">
+        <v>0.1602950367254011</v>
+      </c>
+      <c r="W27">
+        <v>0.1753303963317362</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.5936853212051894</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.152126558373007</v>
+      </c>
+      <c r="C28">
+        <v>29.41359337461587</v>
+      </c>
+      <c r="D28">
+        <v>33.73183633366818</v>
+      </c>
+      <c r="E28">
+        <v>13.97115465500495</v>
+      </c>
+      <c r="F28">
+        <v>15.11824295905231</v>
+      </c>
+      <c r="G28">
+        <v>10.8</v>
+      </c>
+      <c r="H28">
+        <v>57</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.942</v>
+      </c>
+      <c r="K28">
+        <v>1.14</v>
+      </c>
+      <c r="L28">
+        <v>1.802</v>
+      </c>
+      <c r="M28">
+        <v>3.156689129850123</v>
+      </c>
+      <c r="N28">
+        <v>-1.354689129850123</v>
+      </c>
+      <c r="O28">
+        <v>-0.3657660650595334</v>
+      </c>
+      <c r="P28">
+        <v>-0.98892306479059</v>
+      </c>
+      <c r="Q28">
+        <v>0.1510769352094099</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1435215666082066</v>
+      </c>
+      <c r="T28">
+        <v>1.163515911917737</v>
+      </c>
+      <c r="U28">
+        <v>0.2088</v>
+      </c>
+      <c r="V28">
+        <v>0.1541298430051934</v>
+      </c>
+      <c r="W28">
+        <v>0.1766176887805156</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.5708512703896051</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.153826558373007</v>
+      </c>
+      <c r="C29">
+        <v>28.33359308603341</v>
+      </c>
+      <c r="D29">
+        <v>33.23330692812619</v>
+      </c>
+      <c r="E29">
+        <v>14.55262553804543</v>
+      </c>
+      <c r="F29">
+        <v>15.69971384209279</v>
+      </c>
+      <c r="G29">
+        <v>10.8</v>
+      </c>
+      <c r="H29">
+        <v>57</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.942</v>
+      </c>
+      <c r="K29">
+        <v>1.14</v>
+      </c>
+      <c r="L29">
+        <v>1.802</v>
+      </c>
+      <c r="M29">
+        <v>3.278100250228974</v>
+      </c>
+      <c r="N29">
+        <v>-1.476100250228974</v>
+      </c>
+      <c r="O29">
+        <v>-0.3985470675618231</v>
+      </c>
+      <c r="P29">
+        <v>-1.077553182667151</v>
+      </c>
+      <c r="Q29">
+        <v>0.06244681733284874</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1449561086165382</v>
+      </c>
+      <c r="T29">
+        <v>1.179454486053596</v>
+      </c>
+      <c r="U29">
+        <v>0.2088</v>
+      </c>
+      <c r="V29">
+        <v>0.1484213303012973</v>
+      </c>
+      <c r="W29">
+        <v>0.1778096262330891</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.5497086307455457</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.155526558373007</v>
+      </c>
+      <c r="C30">
+        <v>27.26811391417423</v>
+      </c>
+      <c r="D30">
+        <v>32.7492986393075</v>
+      </c>
+      <c r="E30">
+        <v>15.1340964210859</v>
+      </c>
+      <c r="F30">
+        <v>16.28118472513326</v>
+      </c>
+      <c r="G30">
+        <v>10.8</v>
+      </c>
+      <c r="H30">
+        <v>57</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.942</v>
+      </c>
+      <c r="K30">
+        <v>1.14</v>
+      </c>
+      <c r="L30">
+        <v>1.802</v>
+      </c>
+      <c r="M30">
+        <v>3.399511370607825</v>
+      </c>
+      <c r="N30">
+        <v>-1.597511370607825</v>
+      </c>
+      <c r="O30">
+        <v>-0.4313280700641129</v>
+      </c>
+      <c r="P30">
+        <v>-1.166183300543713</v>
+      </c>
+      <c r="Q30">
+        <v>-0.02618330054371265</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1464304990139902</v>
+      </c>
+      <c r="T30">
+        <v>1.195835798359897</v>
+      </c>
+      <c r="U30">
+        <v>0.2088</v>
+      </c>
+      <c r="V30">
+        <v>0.1431205685048224</v>
+      </c>
+      <c r="W30">
+        <v>0.1789164252961931</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.5300761796474904</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.157226558373007</v>
+      </c>
+      <c r="C31">
+        <v>26.21653051201903</v>
+      </c>
+      <c r="D31">
+        <v>32.27918612019276</v>
+      </c>
+      <c r="E31">
+        <v>15.71556730412637</v>
+      </c>
+      <c r="F31">
+        <v>16.86265560817373</v>
+      </c>
+      <c r="G31">
+        <v>10.8</v>
+      </c>
+      <c r="H31">
+        <v>57</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.942</v>
+      </c>
+      <c r="K31">
+        <v>1.14</v>
+      </c>
+      <c r="L31">
+        <v>1.802</v>
+      </c>
+      <c r="M31">
+        <v>3.520922490986675</v>
+      </c>
+      <c r="N31">
+        <v>-1.718922490986676</v>
+      </c>
+      <c r="O31">
+        <v>-0.4641090725664024</v>
+      </c>
+      <c r="P31">
+        <v>-1.254813418420273</v>
+      </c>
+      <c r="Q31">
+        <v>-0.1148134184202732</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.147946421535314</v>
+      </c>
+      <c r="T31">
+        <v>1.212678556083275</v>
+      </c>
+      <c r="U31">
+        <v>0.2088</v>
+      </c>
+      <c r="V31">
+        <v>0.1381853764874148</v>
+      </c>
+      <c r="W31">
+        <v>0.1799468933894278</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5117976906941287</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1683329801802495</v>
+      </c>
+      <c r="C32">
+        <v>22.86737640153736</v>
+      </c>
+      <c r="D32">
+        <v>29.51150289275157</v>
+      </c>
+      <c r="E32">
+        <v>16.29703818716685</v>
+      </c>
+      <c r="F32">
+        <v>17.44412649121421</v>
+      </c>
+      <c r="G32">
+        <v>10.8</v>
+      </c>
+      <c r="H32">
+        <v>57</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.942</v>
+      </c>
+      <c r="K32">
+        <v>1.14</v>
+      </c>
+      <c r="L32">
+        <v>1.802</v>
+      </c>
+      <c r="M32">
+        <v>4.165657406101952</v>
+      </c>
+      <c r="N32">
+        <v>-2.363657406101953</v>
+      </c>
+      <c r="O32">
+        <v>-0.6381874996475273</v>
+      </c>
+      <c r="P32">
+        <v>-1.725469906454426</v>
+      </c>
+      <c r="Q32">
+        <v>-0.5854699064544258</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1500862587104506</v>
+      </c>
+      <c r="T32">
+        <v>1.236453358951718</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.1167978910813224</v>
+      </c>
+      <c r="W32">
+        <v>0.2109086636097802</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.4325847817826756</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1703329801802495</v>
+      </c>
+      <c r="C33">
+        <v>21.83717390985684</v>
+      </c>
+      <c r="D33">
+        <v>29.06277128411152</v>
+      </c>
+      <c r="E33">
+        <v>16.87850907020732</v>
+      </c>
+      <c r="F33">
+        <v>18.02559737425468</v>
+      </c>
+      <c r="G33">
+        <v>10.8</v>
+      </c>
+      <c r="H33">
+        <v>57</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.942</v>
+      </c>
+      <c r="K33">
+        <v>1.14</v>
+      </c>
+      <c r="L33">
+        <v>1.802</v>
+      </c>
+      <c r="M33">
+        <v>4.304512652972018</v>
+      </c>
+      <c r="N33">
+        <v>-2.502512652972018</v>
+      </c>
+      <c r="O33">
+        <v>-0.675678416302445</v>
+      </c>
+      <c r="P33">
+        <v>-1.826834236669573</v>
+      </c>
+      <c r="Q33">
+        <v>-0.6868342366695732</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1516991030395876</v>
+      </c>
+      <c r="T33">
+        <v>1.254372972849569</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.1130302171754733</v>
+      </c>
+      <c r="W33">
+        <v>0.211808384138497</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.4186304339832344</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1723329801802495</v>
+      </c>
+      <c r="C34">
+        <v>20.82041323930648</v>
+      </c>
+      <c r="D34">
+        <v>28.62748149660163</v>
+      </c>
+      <c r="E34">
+        <v>17.4599799532478</v>
+      </c>
+      <c r="F34">
+        <v>18.60706825729515</v>
+      </c>
+      <c r="G34">
+        <v>10.8</v>
+      </c>
+      <c r="H34">
+        <v>57</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.942</v>
+      </c>
+      <c r="K34">
+        <v>1.14</v>
+      </c>
+      <c r="L34">
+        <v>1.802</v>
+      </c>
+      <c r="M34">
+        <v>4.443367899842083</v>
+      </c>
+      <c r="N34">
+        <v>-2.641367899842083</v>
+      </c>
+      <c r="O34">
+        <v>-0.7131693329573625</v>
+      </c>
+      <c r="P34">
+        <v>-1.928198566884721</v>
+      </c>
+      <c r="Q34">
+        <v>-0.7881985668847209</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1533593839666403</v>
+      </c>
+      <c r="T34">
+        <v>1.272819634215004</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.1094980228887398</v>
+      </c>
+      <c r="W34">
+        <v>0.2126518721341689</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.4055482329212583</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1743329801802495</v>
+      </c>
+      <c r="C35">
+        <v>19.81649932493107</v>
+      </c>
+      <c r="D35">
+        <v>28.20503846526669</v>
+      </c>
+      <c r="E35">
+        <v>18.04145083628827</v>
+      </c>
+      <c r="F35">
+        <v>19.18853914033563</v>
+      </c>
+      <c r="G35">
+        <v>10.8</v>
+      </c>
+      <c r="H35">
+        <v>57</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.942</v>
+      </c>
+      <c r="K35">
+        <v>1.14</v>
+      </c>
+      <c r="L35">
+        <v>1.802</v>
+      </c>
+      <c r="M35">
+        <v>4.582223146712148</v>
+      </c>
+      <c r="N35">
+        <v>-2.780223146712149</v>
+      </c>
+      <c r="O35">
+        <v>-0.7506602496122802</v>
+      </c>
+      <c r="P35">
+        <v>-2.029562897099868</v>
+      </c>
+      <c r="Q35">
+        <v>-0.8895628970998686</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1550692255183813</v>
+      </c>
+      <c r="T35">
+        <v>1.291816942188362</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.1061799009830204</v>
+      </c>
+      <c r="W35">
+        <v>0.2134442396452547</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.393258892529705</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1763329801802495</v>
+      </c>
+      <c r="C36">
+        <v>18.82487171543411</v>
+      </c>
+      <c r="D36">
+        <v>27.79488173881022</v>
+      </c>
+      <c r="E36">
+        <v>18.62292171932874</v>
+      </c>
+      <c r="F36">
+        <v>19.7700100233761</v>
+      </c>
+      <c r="G36">
+        <v>10.8</v>
+      </c>
+      <c r="H36">
+        <v>57</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.942</v>
+      </c>
+      <c r="K36">
+        <v>1.14</v>
+      </c>
+      <c r="L36">
+        <v>1.802</v>
+      </c>
+      <c r="M36">
+        <v>4.721078393582213</v>
+      </c>
+      <c r="N36">
+        <v>-2.919078393582214</v>
+      </c>
+      <c r="O36">
+        <v>-0.7881511662671977</v>
+      </c>
+      <c r="P36">
+        <v>-2.130927227315016</v>
+      </c>
+      <c r="Q36">
+        <v>-0.990927227315016</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1568308804504779</v>
+      </c>
+      <c r="T36">
+        <v>1.311389926160913</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.1030569627188139</v>
+      </c>
+      <c r="W36">
+        <v>0.2141899973027472</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.3816924545141255</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1783329801802495</v>
+      </c>
+      <c r="C37">
+        <v>17.84500209249854</v>
+      </c>
+      <c r="D37">
+        <v>27.39648299891511</v>
+      </c>
+      <c r="E37">
+        <v>19.20439260236922</v>
+      </c>
+      <c r="F37">
+        <v>20.35148090641658</v>
+      </c>
+      <c r="G37">
+        <v>10.8</v>
+      </c>
+      <c r="H37">
+        <v>57</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.942</v>
+      </c>
+      <c r="K37">
+        <v>1.14</v>
+      </c>
+      <c r="L37">
+        <v>1.802</v>
+      </c>
+      <c r="M37">
+        <v>4.859933640452279</v>
+      </c>
+      <c r="N37">
+        <v>-3.057933640452279</v>
+      </c>
+      <c r="O37">
+        <v>-0.8256420829221154</v>
+      </c>
+      <c r="P37">
+        <v>-2.232291557530163</v>
+      </c>
+      <c r="Q37">
+        <v>-1.092291557530163</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1586467401497161</v>
+      </c>
+      <c r="T37">
+        <v>1.331565155794158</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.1001124780697049</v>
+      </c>
+      <c r="W37">
+        <v>0.2148931402369545</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3707869558137219</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1803329801802495</v>
+      </c>
+      <c r="C38">
+        <v>16.87639200043379</v>
+      </c>
+      <c r="D38">
+        <v>27.00934378989083</v>
+      </c>
+      <c r="E38">
+        <v>19.78586348540969</v>
+      </c>
+      <c r="F38">
+        <v>20.93295178945705</v>
+      </c>
+      <c r="G38">
+        <v>10.8</v>
+      </c>
+      <c r="H38">
+        <v>57</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.942</v>
+      </c>
+      <c r="K38">
+        <v>1.14</v>
+      </c>
+      <c r="L38">
+        <v>1.802</v>
+      </c>
+      <c r="M38">
+        <v>4.998788887322343</v>
+      </c>
+      <c r="N38">
+        <v>-3.196788887322343</v>
+      </c>
+      <c r="O38">
+        <v>-0.8631329995770327</v>
+      </c>
+      <c r="P38">
+        <v>-2.33365588774531</v>
+      </c>
+      <c r="Q38">
+        <v>-1.193655887745311</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1605193454645554</v>
+      </c>
+      <c r="T38">
+        <v>1.352370861353442</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.09733157590110203</v>
+      </c>
+      <c r="W38">
+        <v>0.2155572196748169</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3604873181522297</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1823329801802495</v>
+      </c>
+      <c r="C39">
+        <v>15.91857076563482</v>
+      </c>
+      <c r="D39">
+        <v>26.63299343813234</v>
+      </c>
+      <c r="E39">
+        <v>20.36733436845016</v>
+      </c>
+      <c r="F39">
+        <v>21.51442267249752</v>
+      </c>
+      <c r="G39">
+        <v>10.8</v>
+      </c>
+      <c r="H39">
+        <v>57</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.942</v>
+      </c>
+      <c r="K39">
+        <v>1.14</v>
+      </c>
+      <c r="L39">
+        <v>1.802</v>
+      </c>
+      <c r="M39">
+        <v>5.137644134192408</v>
+      </c>
+      <c r="N39">
+        <v>-3.335644134192409</v>
+      </c>
+      <c r="O39">
+        <v>-0.9006239162319504</v>
+      </c>
+      <c r="P39">
+        <v>-2.435020217960458</v>
+      </c>
+      <c r="Q39">
+        <v>-1.295020217960458</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1624513985671674</v>
+      </c>
+      <c r="T39">
+        <v>1.373837065501909</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.0947009927686398</v>
+      </c>
+      <c r="W39">
+        <v>0.2161854029268488</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.3507444176616289</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1843329801802495</v>
+      </c>
+      <c r="C40">
+        <v>14.97109358759309</v>
+      </c>
+      <c r="D40">
+        <v>26.26698714313109</v>
+      </c>
+      <c r="E40">
+        <v>20.94880525149064</v>
+      </c>
+      <c r="F40">
+        <v>22.095893555538</v>
+      </c>
+      <c r="G40">
+        <v>10.8</v>
+      </c>
+      <c r="H40">
+        <v>57</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.942</v>
+      </c>
+      <c r="K40">
+        <v>1.14</v>
+      </c>
+      <c r="L40">
+        <v>1.802</v>
+      </c>
+      <c r="M40">
+        <v>5.276499381062474</v>
+      </c>
+      <c r="N40">
+        <v>-3.474499381062475</v>
+      </c>
+      <c r="O40">
+        <v>-0.9381148328868683</v>
+      </c>
+      <c r="P40">
+        <v>-2.536384548175606</v>
+      </c>
+      <c r="Q40">
+        <v>-1.396384548175606</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.164445775963412</v>
+      </c>
+      <c r="T40">
+        <v>1.395995727848714</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.09220886137999137</v>
+      </c>
+      <c r="W40">
+        <v>0.2167805239024581</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.3415143014073754</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1863329801802495</v>
+      </c>
+      <c r="C41">
+        <v>14.03353978518042</v>
+      </c>
+      <c r="D41">
+        <v>25.91090422375889</v>
+      </c>
+      <c r="E41">
+        <v>21.53027613453111</v>
+      </c>
+      <c r="F41">
+        <v>22.67736443857847</v>
+      </c>
+      <c r="G41">
+        <v>10.8</v>
+      </c>
+      <c r="H41">
+        <v>57</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.942</v>
+      </c>
+      <c r="K41">
+        <v>1.14</v>
+      </c>
+      <c r="L41">
+        <v>1.802</v>
+      </c>
+      <c r="M41">
+        <v>5.41535462793254</v>
+      </c>
+      <c r="N41">
+        <v>-3.61335462793254</v>
+      </c>
+      <c r="O41">
+        <v>-0.9756057495417858</v>
+      </c>
+      <c r="P41">
+        <v>-2.637748878390754</v>
+      </c>
+      <c r="Q41">
+        <v>-1.497748878390754</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1665055427824843</v>
+      </c>
+      <c r="T41">
+        <v>1.418880903715086</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.08984453160101723</v>
+      </c>
+      <c r="W41">
+        <v>0.2173451258536771</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3327575244482119</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1883329801802495</v>
+      </c>
+      <c r="C42">
+        <v>13.1055111836684</v>
+      </c>
+      <c r="D42">
+        <v>25.56434650528735</v>
+      </c>
+      <c r="E42">
+        <v>22.11174701757159</v>
+      </c>
+      <c r="F42">
+        <v>23.25883532161895</v>
+      </c>
+      <c r="G42">
+        <v>10.8</v>
+      </c>
+      <c r="H42">
+        <v>57</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.942</v>
+      </c>
+      <c r="K42">
+        <v>1.14</v>
+      </c>
+      <c r="L42">
+        <v>1.802</v>
+      </c>
+      <c r="M42">
+        <v>5.554209874802605</v>
+      </c>
+      <c r="N42">
+        <v>-3.752209874802605</v>
+      </c>
+      <c r="O42">
+        <v>-1.013096666196703</v>
+      </c>
+      <c r="P42">
+        <v>-2.739113208605902</v>
+      </c>
+      <c r="Q42">
+        <v>-1.599113208605902</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1686339684955258</v>
+      </c>
+      <c r="T42">
+        <v>1.442528918777005</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.08759841831099181</v>
+      </c>
+      <c r="W42">
+        <v>0.2178814977073352</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3244385863370066</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1903329801802495</v>
+      </c>
+      <c r="C43">
+        <v>12.18663062948072</v>
+      </c>
+      <c r="D43">
+        <v>25.22693683414014</v>
+      </c>
+      <c r="E43">
+        <v>22.69321790061206</v>
+      </c>
+      <c r="F43">
+        <v>23.84030620465942</v>
+      </c>
+      <c r="G43">
+        <v>10.8</v>
+      </c>
+      <c r="H43">
+        <v>57</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.942</v>
+      </c>
+      <c r="K43">
+        <v>1.14</v>
+      </c>
+      <c r="L43">
+        <v>1.802</v>
+      </c>
+      <c r="M43">
+        <v>5.69306512167267</v>
+      </c>
+      <c r="N43">
+        <v>-3.89106512167267</v>
+      </c>
+      <c r="O43">
+        <v>-1.050587582851621</v>
+      </c>
+      <c r="P43">
+        <v>-2.840477538821049</v>
+      </c>
+      <c r="Q43">
+        <v>-1.700477538821049</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1708345442327381</v>
+      </c>
+      <c r="T43">
+        <v>1.46697856146814</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.08546187152291883</v>
+      </c>
+      <c r="W43">
+        <v>0.218391705080327</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3165254500848845</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1923329801802495</v>
+      </c>
+      <c r="C44">
+        <v>11.27654062103119</v>
+      </c>
+      <c r="D44">
+        <v>24.89831770873108</v>
+      </c>
+      <c r="E44">
+        <v>23.27468878365253</v>
+      </c>
+      <c r="F44">
+        <v>24.42177708769989</v>
+      </c>
+      <c r="G44">
+        <v>10.8</v>
+      </c>
+      <c r="H44">
+        <v>57</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.942</v>
+      </c>
+      <c r="K44">
+        <v>1.14</v>
+      </c>
+      <c r="L44">
+        <v>1.802</v>
+      </c>
+      <c r="M44">
+        <v>5.831920368542734</v>
+      </c>
+      <c r="N44">
+        <v>-4.029920368542735</v>
+      </c>
+      <c r="O44">
+        <v>-1.088078499506538</v>
+      </c>
+      <c r="P44">
+        <v>-2.941841869036196</v>
+      </c>
+      <c r="Q44">
+        <v>-1.801841869036196</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1731110018919232</v>
+      </c>
+      <c r="T44">
+        <v>1.492271295286556</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.08342706505808745</v>
+      </c>
+      <c r="W44">
+        <v>0.2188776168641287</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3089891298447682</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1943329801802495</v>
+      </c>
+      <c r="C45">
+        <v>10.37490204519815</v>
+      </c>
+      <c r="D45">
+        <v>24.57815001593852</v>
+      </c>
+      <c r="E45">
+        <v>23.85615966669301</v>
+      </c>
+      <c r="F45">
+        <v>25.00324797074036</v>
+      </c>
+      <c r="G45">
+        <v>10.8</v>
+      </c>
+      <c r="H45">
+        <v>57</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.942</v>
+      </c>
+      <c r="K45">
+        <v>1.14</v>
+      </c>
+      <c r="L45">
+        <v>1.802</v>
+      </c>
+      <c r="M45">
+        <v>5.9707756154128</v>
+      </c>
+      <c r="N45">
+        <v>-4.1687756154128</v>
+      </c>
+      <c r="O45">
+        <v>-1.125569416161456</v>
+      </c>
+      <c r="P45">
+        <v>-3.043206199251344</v>
+      </c>
+      <c r="Q45">
+        <v>-1.903206199251344</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1754673352584482</v>
+      </c>
+      <c r="T45">
+        <v>1.518451493449478</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.08148690075441099</v>
+      </c>
+      <c r="W45">
+        <v>0.2193409280998466</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.301803336127448</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1963329801802495</v>
+      </c>
+      <c r="C46">
+        <v>9.481393010047359</v>
+      </c>
+      <c r="D46">
+        <v>24.26611186382819</v>
+      </c>
+      <c r="E46">
+        <v>24.43763054973348</v>
+      </c>
+      <c r="F46">
+        <v>25.58471885378084</v>
+      </c>
+      <c r="G46">
+        <v>10.8</v>
+      </c>
+      <c r="H46">
+        <v>57</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.942</v>
+      </c>
+      <c r="K46">
+        <v>1.14</v>
+      </c>
+      <c r="L46">
+        <v>1.802</v>
+      </c>
+      <c r="M46">
+        <v>6.109630862282865</v>
+      </c>
+      <c r="N46">
+        <v>-4.307630862282865</v>
+      </c>
+      <c r="O46">
+        <v>-1.163060332816374</v>
+      </c>
+      <c r="P46">
+        <v>-3.144570529466491</v>
+      </c>
+      <c r="Q46">
+        <v>-2.004570529466491</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1779078233880633</v>
+      </c>
+      <c r="T46">
+        <v>1.545566698689647</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.07963492573726529</v>
+      </c>
+      <c r="W46">
+        <v>0.2197831797339411</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2949441693972787</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1983329801802495</v>
+      </c>
+      <c r="C47">
+        <v>8.595707765356888</v>
+      </c>
+      <c r="D47">
+        <v>23.9618975021782</v>
+      </c>
+      <c r="E47">
+        <v>25.01910143277395</v>
+      </c>
+      <c r="F47">
+        <v>26.16618973682131</v>
+      </c>
+      <c r="G47">
+        <v>10.8</v>
+      </c>
+      <c r="H47">
+        <v>57</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.942</v>
+      </c>
+      <c r="K47">
+        <v>1.14</v>
+      </c>
+      <c r="L47">
+        <v>1.802</v>
+      </c>
+      <c r="M47">
+        <v>6.24848610915293</v>
+      </c>
+      <c r="N47">
+        <v>-4.44648610915293</v>
+      </c>
+      <c r="O47">
+        <v>-1.200551249471291</v>
+      </c>
+      <c r="P47">
+        <v>-3.245934859681639</v>
+      </c>
+      <c r="Q47">
+        <v>-2.105934859681639</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1804370565405735</v>
+      </c>
+      <c r="T47">
+        <v>1.573667911393096</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.07786526072088161</v>
+      </c>
+      <c r="W47">
+        <v>0.2202057757398535</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2883898545217837</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2003329801802495</v>
+      </c>
+      <c r="C48">
+        <v>7.717555703334387</v>
+      </c>
+      <c r="D48">
+        <v>23.66521632319617</v>
+      </c>
+      <c r="E48">
+        <v>25.60057231581443</v>
+      </c>
+      <c r="F48">
+        <v>26.74766061986179</v>
+      </c>
+      <c r="G48">
+        <v>10.8</v>
+      </c>
+      <c r="H48">
+        <v>57</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.942</v>
+      </c>
+      <c r="K48">
+        <v>1.14</v>
+      </c>
+      <c r="L48">
+        <v>1.802</v>
+      </c>
+      <c r="M48">
+        <v>6.387341356022995</v>
+      </c>
+      <c r="N48">
+        <v>-4.585341356022996</v>
+      </c>
+      <c r="O48">
+        <v>-1.238042166126209</v>
+      </c>
+      <c r="P48">
+        <v>-3.347299189896787</v>
+      </c>
+      <c r="Q48">
+        <v>-2.207299189896787</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1830599649950286</v>
+      </c>
+      <c r="T48">
+        <v>1.602809909752227</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.076172537661732</v>
+      </c>
+      <c r="W48">
+        <v>0.2206099980063784</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2821205098582666</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2023329801802495</v>
+      </c>
+      <c r="C49">
+        <v>6.846660432661377</v>
+      </c>
+      <c r="D49">
+        <v>23.37579193556363</v>
+      </c>
+      <c r="E49">
+        <v>26.1820431988549</v>
+      </c>
+      <c r="F49">
+        <v>27.32913150290226</v>
+      </c>
+      <c r="G49">
+        <v>10.8</v>
+      </c>
+      <c r="H49">
+        <v>57</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.942</v>
+      </c>
+      <c r="K49">
+        <v>1.14</v>
+      </c>
+      <c r="L49">
+        <v>1.802</v>
+      </c>
+      <c r="M49">
+        <v>6.52619660289306</v>
+      </c>
+      <c r="N49">
+        <v>-4.724196602893061</v>
+      </c>
+      <c r="O49">
+        <v>-1.275533082781126</v>
+      </c>
+      <c r="P49">
+        <v>-3.448663520111935</v>
+      </c>
+      <c r="Q49">
+        <v>-2.308663520111935</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1857818511270103</v>
+      </c>
+      <c r="T49">
+        <v>1.633051606162646</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.07455184537105686</v>
+      </c>
+      <c r="W49">
+        <v>0.2209970193253916</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2761179458187291</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2043329801802495</v>
+      </c>
+      <c r="C50">
+        <v>5.982758919662942</v>
+      </c>
+      <c r="D50">
+        <v>23.09336130560567</v>
+      </c>
+      <c r="E50">
+        <v>26.76351408189537</v>
+      </c>
+      <c r="F50">
+        <v>27.91060238594273</v>
+      </c>
+      <c r="G50">
+        <v>10.8</v>
+      </c>
+      <c r="H50">
+        <v>57</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.942</v>
+      </c>
+      <c r="K50">
+        <v>1.14</v>
+      </c>
+      <c r="L50">
+        <v>1.802</v>
+      </c>
+      <c r="M50">
+        <v>6.665051849763125</v>
+      </c>
+      <c r="N50">
+        <v>-4.863051849763125</v>
+      </c>
+      <c r="O50">
+        <v>-1.313023999436044</v>
+      </c>
+      <c r="P50">
+        <v>-3.550027850327081</v>
+      </c>
+      <c r="Q50">
+        <v>-2.410027850327081</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1886084251871451</v>
+      </c>
+      <c r="T50">
+        <v>1.664456444742697</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.07299868192582651</v>
+      </c>
+      <c r="W50">
+        <v>0.2213679147561126</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2703654886141722</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2063329801802495</v>
+      </c>
+      <c r="C51">
+        <v>5.125600690993451</v>
+      </c>
+      <c r="D51">
+        <v>22.81767395997666</v>
+      </c>
+      <c r="E51">
+        <v>27.34498496493585</v>
+      </c>
+      <c r="F51">
+        <v>28.49207326898321</v>
+      </c>
+      <c r="G51">
+        <v>10.8</v>
+      </c>
+      <c r="H51">
+        <v>57</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.942</v>
+      </c>
+      <c r="K51">
+        <v>1.14</v>
+      </c>
+      <c r="L51">
+        <v>1.802</v>
+      </c>
+      <c r="M51">
+        <v>6.80390709663319</v>
+      </c>
+      <c r="N51">
+        <v>-5.00190709663319</v>
+      </c>
+      <c r="O51">
+        <v>-1.350514916090962</v>
+      </c>
+      <c r="P51">
+        <v>-3.651392180542229</v>
+      </c>
+      <c r="Q51">
+        <v>-2.511392180542229</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1915458452888538</v>
+      </c>
+      <c r="T51">
+        <v>1.697092845620005</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.07150891290693209</v>
+      </c>
+      <c r="W51">
+        <v>0.2217236715978246</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2648478255812299</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2083329801802495</v>
+      </c>
+      <c r="C52">
+        <v>4.274947092758374</v>
+      </c>
+      <c r="D52">
+        <v>22.54849124478205</v>
+      </c>
+      <c r="E52">
+        <v>27.92645584797632</v>
+      </c>
+      <c r="F52">
+        <v>29.07354415202368</v>
+      </c>
+      <c r="G52">
+        <v>10.8</v>
+      </c>
+      <c r="H52">
+        <v>57</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.942</v>
+      </c>
+      <c r="K52">
+        <v>1.14</v>
+      </c>
+      <c r="L52">
+        <v>1.802</v>
+      </c>
+      <c r="M52">
+        <v>6.942762343503255</v>
+      </c>
+      <c r="N52">
+        <v>-5.140762343503256</v>
+      </c>
+      <c r="O52">
+        <v>-1.388005832745879</v>
+      </c>
+      <c r="P52">
+        <v>-3.752756510757377</v>
+      </c>
+      <c r="Q52">
+        <v>-2.612756510757377</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1946007621946309</v>
+      </c>
+      <c r="T52">
+        <v>1.731034702532405</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.07007873464879344</v>
+      </c>
+      <c r="W52">
+        <v>0.2220651981658681</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2595508690696053</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2103329801802495</v>
+      </c>
+      <c r="C53">
+        <v>3.430570601465917</v>
+      </c>
+      <c r="D53">
+        <v>22.28558563653007</v>
+      </c>
+      <c r="E53">
+        <v>28.50792673101679</v>
+      </c>
+      <c r="F53">
+        <v>29.65501503506415</v>
+      </c>
+      <c r="G53">
+        <v>10.8</v>
+      </c>
+      <c r="H53">
+        <v>57</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.942</v>
+      </c>
+      <c r="K53">
+        <v>1.14</v>
+      </c>
+      <c r="L53">
+        <v>1.802</v>
+      </c>
+      <c r="M53">
+        <v>7.081617590373321</v>
+      </c>
+      <c r="N53">
+        <v>-5.279617590373321</v>
+      </c>
+      <c r="O53">
+        <v>-1.425496749400797</v>
+      </c>
+      <c r="P53">
+        <v>-3.854120840972524</v>
+      </c>
+      <c r="Q53">
+        <v>-2.714120840972524</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1977803695863581</v>
+      </c>
+      <c r="T53">
+        <v>1.766361941359597</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.06870464181254259</v>
+      </c>
+      <c r="W53">
+        <v>0.2223933315351649</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2544616363427503</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2123329801802495</v>
+      </c>
+      <c r="C54">
+        <v>2.592254182627201</v>
+      </c>
+      <c r="D54">
+        <v>22.02874010073183</v>
+      </c>
+      <c r="E54">
+        <v>29.08939761405727</v>
+      </c>
+      <c r="F54">
+        <v>30.23648591810463</v>
+      </c>
+      <c r="G54">
+        <v>10.8</v>
+      </c>
+      <c r="H54">
+        <v>57</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.942</v>
+      </c>
+      <c r="K54">
+        <v>1.14</v>
+      </c>
+      <c r="L54">
+        <v>1.802</v>
+      </c>
+      <c r="M54">
+        <v>7.220472837243386</v>
+      </c>
+      <c r="N54">
+        <v>-5.418472837243386</v>
+      </c>
+      <c r="O54">
+        <v>-1.462987666055714</v>
+      </c>
+      <c r="P54">
+        <v>-3.955485171187672</v>
+      </c>
+      <c r="Q54">
+        <v>-2.815485171187672</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2010924606194072</v>
+      </c>
+      <c r="T54">
+        <v>1.803161148471256</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.06738339870076293</v>
+      </c>
+      <c r="W54">
+        <v>0.2227088443902578</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.249568143336159</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2143329801802495</v>
+      </c>
+      <c r="C55">
+        <v>1.759790693204607</v>
+      </c>
+      <c r="D55">
+        <v>21.7777474943497</v>
+      </c>
+      <c r="E55">
+        <v>29.67086849709774</v>
+      </c>
+      <c r="F55">
+        <v>30.8179568011451</v>
+      </c>
+      <c r="G55">
+        <v>10.8</v>
+      </c>
+      <c r="H55">
+        <v>57</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.942</v>
+      </c>
+      <c r="K55">
+        <v>1.14</v>
+      </c>
+      <c r="L55">
+        <v>1.802</v>
+      </c>
+      <c r="M55">
+        <v>7.35932808411345</v>
+      </c>
+      <c r="N55">
+        <v>-5.55732808411345</v>
+      </c>
+      <c r="O55">
+        <v>-1.500478582710632</v>
+      </c>
+      <c r="P55">
+        <v>-4.056849501402819</v>
+      </c>
+      <c r="Q55">
+        <v>-2.916849501402819</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2045454916964158</v>
+      </c>
+      <c r="T55">
+        <v>1.841526279289793</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.06611201381961647</v>
+      </c>
+      <c r="W55">
+        <v>0.2230124510998756</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2448593104430239</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2163329801802495</v>
+      </c>
+      <c r="C56">
+        <v>0.9329823244503288</v>
+      </c>
+      <c r="D56">
+        <v>21.5324100086359</v>
+      </c>
+      <c r="E56">
+        <v>30.25233938013822</v>
+      </c>
+      <c r="F56">
+        <v>31.39942768418558</v>
+      </c>
+      <c r="G56">
+        <v>10.8</v>
+      </c>
+      <c r="H56">
+        <v>57</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.942</v>
+      </c>
+      <c r="K56">
+        <v>1.14</v>
+      </c>
+      <c r="L56">
+        <v>1.802</v>
+      </c>
+      <c r="M56">
+        <v>7.498183330983515</v>
+      </c>
+      <c r="N56">
+        <v>-5.696183330983516</v>
+      </c>
+      <c r="O56">
+        <v>-1.537969499365549</v>
+      </c>
+      <c r="P56">
+        <v>-4.158213831617966</v>
+      </c>
+      <c r="Q56">
+        <v>-3.018213831617967</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2081486545593814</v>
+      </c>
+      <c r="T56">
+        <v>1.881559459274354</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.06488771726740135</v>
+      </c>
+      <c r="W56">
+        <v>0.2233048131165446</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2403248787681531</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2183329801802495</v>
+      </c>
+      <c r="C57">
+        <v>0.1116400819858967</v>
+      </c>
+      <c r="D57">
+        <v>21.29253864921194</v>
+      </c>
+      <c r="E57">
+        <v>30.83381026317869</v>
+      </c>
+      <c r="F57">
+        <v>31.98089856722605</v>
+      </c>
+      <c r="G57">
+        <v>10.8</v>
+      </c>
+      <c r="H57">
+        <v>57</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.942</v>
+      </c>
+      <c r="K57">
+        <v>1.14</v>
+      </c>
+      <c r="L57">
+        <v>1.802</v>
+      </c>
+      <c r="M57">
+        <v>7.637038577853581</v>
+      </c>
+      <c r="N57">
+        <v>-5.835038577853581</v>
+      </c>
+      <c r="O57">
+        <v>-1.575460416020467</v>
+      </c>
+      <c r="P57">
+        <v>-4.259578161833113</v>
+      </c>
+      <c r="Q57">
+        <v>-3.119578161833114</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2119119579940343</v>
+      </c>
+      <c r="T57">
+        <v>1.923371891702673</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.06370794058981223</v>
+      </c>
+      <c r="W57">
+        <v>0.2235865437871528</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.235955335517823</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2203329801802495</v>
+      </c>
+      <c r="C58">
+        <v>-0.7044166997499026</v>
+      </c>
+      <c r="D58">
+        <v>21.05795275051662</v>
+      </c>
+      <c r="E58">
+        <v>31.41528114621917</v>
+      </c>
+      <c r="F58">
+        <v>32.56236945026652</v>
+      </c>
+      <c r="G58">
+        <v>10.8</v>
+      </c>
+      <c r="H58">
+        <v>57</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.942</v>
+      </c>
+      <c r="K58">
+        <v>1.14</v>
+      </c>
+      <c r="L58">
+        <v>1.802</v>
+      </c>
+      <c r="M58">
+        <v>7.775893824723646</v>
+      </c>
+      <c r="N58">
+        <v>-5.973893824723646</v>
+      </c>
+      <c r="O58">
+        <v>-1.612951332675385</v>
+      </c>
+      <c r="P58">
+        <v>-4.360942492048261</v>
+      </c>
+      <c r="Q58">
+        <v>-3.220942492048262</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2158463206757169</v>
+      </c>
+      <c r="T58">
+        <v>1.967084889241369</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.06257029879356558</v>
+      </c>
+      <c r="W58">
+        <v>0.2238582126480965</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2317418473835762</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2223329801802495</v>
+      </c>
+      <c r="C59">
+        <v>-1.515360811305872</v>
+      </c>
+      <c r="D59">
+        <v>20.82847952200112</v>
+      </c>
+      <c r="E59">
+        <v>31.99675202925964</v>
+      </c>
+      <c r="F59">
+        <v>33.143840333307</v>
+      </c>
+      <c r="G59">
+        <v>10.8</v>
+      </c>
+      <c r="H59">
+        <v>57</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.942</v>
+      </c>
+      <c r="K59">
+        <v>1.14</v>
+      </c>
+      <c r="L59">
+        <v>1.802</v>
+      </c>
+      <c r="M59">
+        <v>7.914749071593711</v>
+      </c>
+      <c r="N59">
+        <v>-6.112749071593711</v>
+      </c>
+      <c r="O59">
+        <v>-1.650442249330302</v>
+      </c>
+      <c r="P59">
+        <v>-4.462306822263409</v>
+      </c>
+      <c r="Q59">
+        <v>-3.32230682226341</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.219963676970501</v>
+      </c>
+      <c r="T59">
+        <v>2.012831049456285</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.06147257425332759</v>
+      </c>
+      <c r="W59">
+        <v>0.2241203492683054</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2276762009382503</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2243329801802495</v>
+      </c>
+      <c r="C60">
+        <v>-2.321357592671973</v>
+      </c>
+      <c r="D60">
+        <v>20.60395362367549</v>
+      </c>
+      <c r="E60">
+        <v>32.57822291230011</v>
+      </c>
+      <c r="F60">
+        <v>33.72531121634746</v>
+      </c>
+      <c r="G60">
+        <v>10.8</v>
+      </c>
+      <c r="H60">
+        <v>57</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.942</v>
+      </c>
+      <c r="K60">
+        <v>1.14</v>
+      </c>
+      <c r="L60">
+        <v>1.802</v>
+      </c>
+      <c r="M60">
+        <v>8.053604318463774</v>
+      </c>
+      <c r="N60">
+        <v>-6.251604318463775</v>
+      </c>
+      <c r="O60">
+        <v>-1.687933165985219</v>
+      </c>
+      <c r="P60">
+        <v>-4.563671152478555</v>
+      </c>
+      <c r="Q60">
+        <v>-3.423671152478556</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.224277097850751</v>
+      </c>
+      <c r="T60">
+        <v>2.060755598252863</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.06041270228344264</v>
+      </c>
+      <c r="W60">
+        <v>0.2243734466947139</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2237507491979357</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2263329801802495</v>
+      </c>
+      <c r="C61">
+        <v>-3.122565330572552</v>
+      </c>
+      <c r="D61">
+        <v>20.38421676881539</v>
+      </c>
+      <c r="E61">
+        <v>33.15969379534058</v>
+      </c>
+      <c r="F61">
+        <v>34.30678209938794</v>
+      </c>
+      <c r="G61">
+        <v>10.8</v>
+      </c>
+      <c r="H61">
+        <v>57</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.942</v>
+      </c>
+      <c r="K61">
+        <v>1.14</v>
+      </c>
+      <c r="L61">
+        <v>1.802</v>
+      </c>
+      <c r="M61">
+        <v>8.19245956533384</v>
+      </c>
+      <c r="N61">
+        <v>-6.39045956533384</v>
+      </c>
+      <c r="O61">
+        <v>-1.725424082640137</v>
+      </c>
+      <c r="P61">
+        <v>-4.665035482693703</v>
+      </c>
+      <c r="Q61">
+        <v>-3.525035482693704</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2288009295056474</v>
+      </c>
+      <c r="T61">
+        <v>2.111017929917567</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.05938875817694361</v>
+      </c>
+      <c r="W61">
+        <v>0.2246179645473459</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2199583636183097</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2283329801802495</v>
+      </c>
+      <c r="C62">
+        <v>-3.919135630605574</v>
+      </c>
+      <c r="D62">
+        <v>20.16911735182284</v>
+      </c>
+      <c r="E62">
+        <v>33.74116467838105</v>
+      </c>
+      <c r="F62">
+        <v>34.88825298242841</v>
+      </c>
+      <c r="G62">
+        <v>10.8</v>
+      </c>
+      <c r="H62">
+        <v>57</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.942</v>
+      </c>
+      <c r="K62">
+        <v>1.14</v>
+      </c>
+      <c r="L62">
+        <v>1.802</v>
+      </c>
+      <c r="M62">
+        <v>8.331314812203905</v>
+      </c>
+      <c r="N62">
+        <v>-6.529314812203905</v>
+      </c>
+      <c r="O62">
+        <v>-1.762914999295055</v>
+      </c>
+      <c r="P62">
+        <v>-4.766399812908851</v>
+      </c>
+      <c r="Q62">
+        <v>-3.626399812908851</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2335509527432886</v>
+      </c>
+      <c r="T62">
+        <v>2.163793378165507</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.05839894554066122</v>
+      </c>
+      <c r="W62">
+        <v>0.2248543318048901</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2162923908913378</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2303329801802495</v>
+      </c>
+      <c r="C63">
+        <v>-4.711213766066408</v>
+      </c>
+      <c r="D63">
+        <v>19.95851009940248</v>
+      </c>
+      <c r="E63">
+        <v>34.32263556142153</v>
+      </c>
+      <c r="F63">
+        <v>35.46972386546889</v>
+      </c>
+      <c r="G63">
+        <v>10.8</v>
+      </c>
+      <c r="H63">
+        <v>57</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.942</v>
+      </c>
+      <c r="K63">
+        <v>1.14</v>
+      </c>
+      <c r="L63">
+        <v>1.802</v>
+      </c>
+      <c r="M63">
+        <v>8.47017005907397</v>
+      </c>
+      <c r="N63">
+        <v>-6.668170059073971</v>
+      </c>
+      <c r="O63">
+        <v>-1.800405915949972</v>
+      </c>
+      <c r="P63">
+        <v>-4.867764143123998</v>
+      </c>
+      <c r="Q63">
+        <v>-3.727764143123999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2385445669161935</v>
+      </c>
+      <c r="T63">
+        <v>2.21927525965693</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.05744158577769955</v>
+      </c>
+      <c r="W63">
+        <v>0.2250829493162854</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2127466139914798</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2323329801802495</v>
+      </c>
+      <c r="C64">
+        <v>-5.498939005142876</v>
+      </c>
+      <c r="D64">
+        <v>19.75225574336648</v>
+      </c>
+      <c r="E64">
+        <v>34.904106444462</v>
+      </c>
+      <c r="F64">
+        <v>36.05119474850936</v>
+      </c>
+      <c r="G64">
+        <v>10.8</v>
+      </c>
+      <c r="H64">
+        <v>57</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.942</v>
+      </c>
+      <c r="K64">
+        <v>1.14</v>
+      </c>
+      <c r="L64">
+        <v>1.802</v>
+      </c>
+      <c r="M64">
+        <v>8.609025305944035</v>
+      </c>
+      <c r="N64">
+        <v>-6.807025305944036</v>
+      </c>
+      <c r="O64">
+        <v>-1.83789683260489</v>
+      </c>
+      <c r="P64">
+        <v>-4.969128473339146</v>
+      </c>
+      <c r="Q64">
+        <v>-3.829128473339146</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2438010028876722</v>
+      </c>
+      <c r="T64">
+        <v>2.277677240174217</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.05651510858773667</v>
+      </c>
+      <c r="W64">
+        <v>0.2253041920692485</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2093152169916173</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2343329801802495</v>
+      </c>
+      <c r="C65">
+        <v>-6.282444918030066</v>
+      </c>
+      <c r="D65">
+        <v>19.55022071351977</v>
+      </c>
+      <c r="E65">
+        <v>35.48557732750248</v>
+      </c>
+      <c r="F65">
+        <v>36.63266563154983</v>
+      </c>
+      <c r="G65">
+        <v>10.8</v>
+      </c>
+      <c r="H65">
+        <v>57</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.942</v>
+      </c>
+      <c r="K65">
+        <v>1.14</v>
+      </c>
+      <c r="L65">
+        <v>1.802</v>
+      </c>
+      <c r="M65">
+        <v>8.747880552814101</v>
+      </c>
+      <c r="N65">
+        <v>-6.945880552814101</v>
+      </c>
+      <c r="O65">
+        <v>-1.875387749259807</v>
+      </c>
+      <c r="P65">
+        <v>-5.070492803554293</v>
+      </c>
+      <c r="Q65">
+        <v>-3.930492803554293</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.249341570533285</v>
+      </c>
+      <c r="T65">
+        <v>2.33923608450325</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.0556180433720583</v>
+      </c>
+      <c r="W65">
+        <v>0.2255184112427525</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2059927532298456</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2363329801802496</v>
+      </c>
+      <c r="C66">
+        <v>-7.061859665388088</v>
+      </c>
+      <c r="D66">
+        <v>19.35227684920222</v>
+      </c>
+      <c r="E66">
+        <v>36.06704821054295</v>
+      </c>
+      <c r="F66">
+        <v>37.21413651459031</v>
+      </c>
+      <c r="G66">
+        <v>10.8</v>
+      </c>
+      <c r="H66">
+        <v>57</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.942</v>
+      </c>
+      <c r="K66">
+        <v>1.14</v>
+      </c>
+      <c r="L66">
+        <v>1.802</v>
+      </c>
+      <c r="M66">
+        <v>8.886735799684166</v>
+      </c>
+      <c r="N66">
+        <v>-7.084735799684166</v>
+      </c>
+      <c r="O66">
+        <v>-1.912878665914725</v>
+      </c>
+      <c r="P66">
+        <v>-5.171857133769441</v>
+      </c>
+      <c r="Q66">
+        <v>-4.031857133769441</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.255189947492543</v>
+      </c>
+      <c r="T66">
+        <v>2.404214864628341</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.05474901144436989</v>
+      </c>
+      <c r="W66">
+        <v>0.2257259360670845</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2027741164606292</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2383329801802495</v>
+      </c>
+      <c r="C67">
+        <v>-7.837306269451918</v>
+      </c>
+      <c r="D67">
+        <v>19.15830112817886</v>
+      </c>
+      <c r="E67">
+        <v>36.64851909358342</v>
+      </c>
+      <c r="F67">
+        <v>37.79560739763078</v>
+      </c>
+      <c r="G67">
+        <v>10.8</v>
+      </c>
+      <c r="H67">
+        <v>57</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.942</v>
+      </c>
+      <c r="K67">
+        <v>1.14</v>
+      </c>
+      <c r="L67">
+        <v>1.802</v>
+      </c>
+      <c r="M67">
+        <v>9.025591046554231</v>
+      </c>
+      <c r="N67">
+        <v>-7.223591046554231</v>
+      </c>
+      <c r="O67">
+        <v>-1.950369582569643</v>
+      </c>
+      <c r="P67">
+        <v>-5.273221463984589</v>
+      </c>
+      <c r="Q67">
+        <v>-4.133221463984589</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2613725174209013</v>
+      </c>
+      <c r="T67">
+        <v>2.472906717903436</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.05390671896061035</v>
+      </c>
+      <c r="W67">
+        <v>0.2259270755122063</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1996545146689271</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2403329801802495</v>
+      </c>
+      <c r="C68">
+        <v>-8.608902868998385</v>
+      </c>
+      <c r="D68">
+        <v>18.96817541167287</v>
+      </c>
+      <c r="E68">
+        <v>37.2299899766239</v>
+      </c>
+      <c r="F68">
+        <v>38.37707828067126</v>
+      </c>
+      <c r="G68">
+        <v>10.8</v>
+      </c>
+      <c r="H68">
+        <v>57</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.942</v>
+      </c>
+      <c r="K68">
+        <v>1.14</v>
+      </c>
+      <c r="L68">
+        <v>1.802</v>
+      </c>
+      <c r="M68">
+        <v>9.164446293424296</v>
+      </c>
+      <c r="N68">
+        <v>-7.362446293424297</v>
+      </c>
+      <c r="O68">
+        <v>-1.98786049922456</v>
+      </c>
+      <c r="P68">
+        <v>-5.374585794199737</v>
+      </c>
+      <c r="Q68">
+        <v>-4.234585794199737</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2679187679332807</v>
+      </c>
+      <c r="T68">
+        <v>2.545639268430008</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.05308995049151019</v>
+      </c>
+      <c r="W68">
+        <v>0.2261221198226274</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1966294462648526</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2423329801802495</v>
+      </c>
+      <c r="C69">
+        <v>-9.376762959280601</v>
+      </c>
+      <c r="D69">
+        <v>18.78178620443113</v>
+      </c>
+      <c r="E69">
+        <v>37.81146085966437</v>
+      </c>
+      <c r="F69">
+        <v>38.95854916371173</v>
+      </c>
+      <c r="G69">
+        <v>10.8</v>
+      </c>
+      <c r="H69">
+        <v>57</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.942</v>
+      </c>
+      <c r="K69">
+        <v>1.14</v>
+      </c>
+      <c r="L69">
+        <v>1.802</v>
+      </c>
+      <c r="M69">
+        <v>9.303301540294362</v>
+      </c>
+      <c r="N69">
+        <v>-7.501301540294362</v>
+      </c>
+      <c r="O69">
+        <v>-2.025351415879478</v>
+      </c>
+      <c r="P69">
+        <v>-5.475950124414885</v>
+      </c>
+      <c r="Q69">
+        <v>-4.335950124414885</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2748617609009559</v>
+      </c>
+      <c r="T69">
+        <v>2.622779852321826</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.05229756317074138</v>
+      </c>
+      <c r="W69">
+        <v>0.226311341914827</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1936946784101532</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2443329801802496</v>
+      </c>
+      <c r="C70">
+        <v>-10.14099561795397</v>
+      </c>
+      <c r="D70">
+        <v>18.59902442879823</v>
+      </c>
+      <c r="E70">
+        <v>38.39293174270485</v>
+      </c>
+      <c r="F70">
+        <v>39.5400200467522</v>
+      </c>
+      <c r="G70">
+        <v>10.8</v>
+      </c>
+      <c r="H70">
+        <v>57</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.942</v>
+      </c>
+      <c r="K70">
+        <v>1.14</v>
+      </c>
+      <c r="L70">
+        <v>1.802</v>
+      </c>
+      <c r="M70">
+        <v>9.442156787164427</v>
+      </c>
+      <c r="N70">
+        <v>-7.640156787164427</v>
+      </c>
+      <c r="O70">
+        <v>-2.062842332534395</v>
+      </c>
+      <c r="P70">
+        <v>-5.577314454630032</v>
+      </c>
+      <c r="Q70">
+        <v>-4.437314454630032</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2822386909291108</v>
+      </c>
+      <c r="T70">
+        <v>2.704741722706884</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.05152848135940695</v>
+      </c>
+      <c r="W70">
+        <v>0.2264949986513737</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1908462272570628</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2463329801802495</v>
+      </c>
+      <c r="C71">
+        <v>-10.9017057179386</v>
+      </c>
+      <c r="D71">
+        <v>18.41978521185407</v>
+      </c>
+      <c r="E71">
+        <v>38.97440262574532</v>
+      </c>
+      <c r="F71">
+        <v>40.12149092979268</v>
+      </c>
+      <c r="G71">
+        <v>10.8</v>
+      </c>
+      <c r="H71">
+        <v>57</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.942</v>
+      </c>
+      <c r="K71">
+        <v>1.14</v>
+      </c>
+      <c r="L71">
+        <v>1.802</v>
+      </c>
+      <c r="M71">
+        <v>9.581012034034492</v>
+      </c>
+      <c r="N71">
+        <v>-7.779012034034492</v>
+      </c>
+      <c r="O71">
+        <v>-2.100333249189313</v>
+      </c>
+      <c r="P71">
+        <v>-5.678678784845179</v>
+      </c>
+      <c r="Q71">
+        <v>-4.538678784845179</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2900915519268241</v>
+      </c>
+      <c r="T71">
+        <v>2.791991455697428</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.05078169177448801</v>
+      </c>
+      <c r="W71">
+        <v>0.2266733320042523</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1880803399055111</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2483329801802495</v>
+      </c>
+      <c r="C72">
+        <v>-11.65899412809112</v>
+      </c>
+      <c r="D72">
+        <v>18.24396768474203</v>
+      </c>
+      <c r="E72">
+        <v>39.55587350878579</v>
+      </c>
+      <c r="F72">
+        <v>40.70296181283315</v>
+      </c>
+      <c r="G72">
+        <v>10.8</v>
+      </c>
+      <c r="H72">
+        <v>57</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.942</v>
+      </c>
+      <c r="K72">
+        <v>1.14</v>
+      </c>
+      <c r="L72">
+        <v>1.802</v>
+      </c>
+      <c r="M72">
+        <v>9.719867280904557</v>
+      </c>
+      <c r="N72">
+        <v>-7.917867280904558</v>
+      </c>
+      <c r="O72">
+        <v>-2.137824165844231</v>
+      </c>
+      <c r="P72">
+        <v>-5.780043115060327</v>
+      </c>
+      <c r="Q72">
+        <v>-4.640043115060327</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2984679369910515</v>
+      </c>
+      <c r="T72">
+        <v>2.885057837554009</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.05005623903485246</v>
+      </c>
+      <c r="W72">
+        <v>0.2268465701184773</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1853934779068609</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2503329801802495</v>
+      </c>
+      <c r="C73">
+        <v>-12.41295790249251</v>
+      </c>
+      <c r="D73">
+        <v>18.07147479338111</v>
+      </c>
+      <c r="E73">
+        <v>40.13734439182626</v>
+      </c>
+      <c r="F73">
+        <v>41.28443269587362</v>
+      </c>
+      <c r="G73">
+        <v>10.8</v>
+      </c>
+      <c r="H73">
+        <v>57</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.942</v>
+      </c>
+      <c r="K73">
+        <v>1.14</v>
+      </c>
+      <c r="L73">
+        <v>1.802</v>
+      </c>
+      <c r="M73">
+        <v>9.858722527774621</v>
+      </c>
+      <c r="N73">
+        <v>-8.056722527774621</v>
+      </c>
+      <c r="O73">
+        <v>-2.175315082499148</v>
+      </c>
+      <c r="P73">
+        <v>-5.881407445275473</v>
+      </c>
+      <c r="Q73">
+        <v>-4.741407445275473</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3074220037838463</v>
+      </c>
+      <c r="T73">
+        <v>2.984542590573112</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.04935122158365737</v>
+      </c>
+      <c r="W73">
+        <v>0.2270149282858226</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1827823021616939</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2523329801802495</v>
+      </c>
+      <c r="C74">
+        <v>-13.1636904590986</v>
+      </c>
+      <c r="D74">
+        <v>17.90221311981549</v>
+      </c>
+      <c r="E74">
+        <v>40.71881527486673</v>
+      </c>
+      <c r="F74">
+        <v>41.86590357891409</v>
+      </c>
+      <c r="G74">
+        <v>10.8</v>
+      </c>
+      <c r="H74">
+        <v>57</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.942</v>
+      </c>
+      <c r="K74">
+        <v>1.14</v>
+      </c>
+      <c r="L74">
+        <v>1.802</v>
+      </c>
+      <c r="M74">
+        <v>9.997577774644686</v>
+      </c>
+      <c r="N74">
+        <v>-8.195577774644686</v>
+      </c>
+      <c r="O74">
+        <v>-2.212805999154066</v>
+      </c>
+      <c r="P74">
+        <v>-5.982771775490621</v>
+      </c>
+      <c r="Q74">
+        <v>-4.842771775490621</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3170156467761266</v>
+      </c>
+      <c r="T74">
+        <v>3.091133397379295</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.04866578795055101</v>
+      </c>
+      <c r="W74">
+        <v>0.2271786098374084</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1802436590761148</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2543329801802495</v>
+      </c>
+      <c r="C75">
+        <v>-13.91128174844389</v>
+      </c>
+      <c r="D75">
+        <v>17.73609271351067</v>
+      </c>
+      <c r="E75">
+        <v>41.30028615790721</v>
+      </c>
+      <c r="F75">
+        <v>42.44737446195457</v>
+      </c>
+      <c r="G75">
+        <v>10.8</v>
+      </c>
+      <c r="H75">
+        <v>57</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.942</v>
+      </c>
+      <c r="K75">
+        <v>1.14</v>
+      </c>
+      <c r="L75">
+        <v>1.802</v>
+      </c>
+      <c r="M75">
+        <v>10.13643302151475</v>
+      </c>
+      <c r="N75">
+        <v>-8.334433021514752</v>
+      </c>
+      <c r="O75">
+        <v>-2.250296915808983</v>
+      </c>
+      <c r="P75">
+        <v>-6.084136105705769</v>
+      </c>
+      <c r="Q75">
+        <v>-4.944136105705769</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3273199299900572</v>
+      </c>
+      <c r="T75">
+        <v>3.205619819504454</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04799913332109141</v>
+      </c>
+      <c r="W75">
+        <v>0.2273378069629234</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1777745678558941</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2563329801802495</v>
+      </c>
+      <c r="C76">
+        <v>-14.65581841303909</v>
+      </c>
+      <c r="D76">
+        <v>17.57302693195595</v>
+      </c>
+      <c r="E76">
+        <v>41.88175704094768</v>
+      </c>
+      <c r="F76">
+        <v>43.02884534499504</v>
+      </c>
+      <c r="G76">
+        <v>10.8</v>
+      </c>
+      <c r="H76">
+        <v>57</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.942</v>
+      </c>
+      <c r="K76">
+        <v>1.14</v>
+      </c>
+      <c r="L76">
+        <v>1.802</v>
+      </c>
+      <c r="M76">
+        <v>10.27528826838482</v>
+      </c>
+      <c r="N76">
+        <v>-8.473288268384817</v>
+      </c>
+      <c r="O76">
+        <v>-2.287787832463901</v>
+      </c>
+      <c r="P76">
+        <v>-6.185500435920916</v>
+      </c>
+      <c r="Q76">
+        <v>-5.045500435920917</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3384168503742901</v>
+      </c>
+      <c r="T76">
+        <v>3.328912889485395</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0473504963843199</v>
+      </c>
+      <c r="W76">
+        <v>0.2274927014634244</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1753722088308144</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2583329801802495</v>
+      </c>
+      <c r="C77">
+        <v>-15.39738393805571</v>
+      </c>
+      <c r="D77">
+        <v>17.41293228997981</v>
+      </c>
+      <c r="E77">
+        <v>42.46322792398816</v>
+      </c>
+      <c r="F77">
+        <v>43.61031622803551</v>
+      </c>
+      <c r="G77">
+        <v>10.8</v>
+      </c>
+      <c r="H77">
+        <v>57</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.942</v>
+      </c>
+      <c r="K77">
+        <v>1.14</v>
+      </c>
+      <c r="L77">
+        <v>1.802</v>
+      </c>
+      <c r="M77">
+        <v>10.41414351525488</v>
+      </c>
+      <c r="N77">
+        <v>-8.612143515254882</v>
+      </c>
+      <c r="O77">
+        <v>-2.325278749118818</v>
+      </c>
+      <c r="P77">
+        <v>-6.286864766136063</v>
+      </c>
+      <c r="Q77">
+        <v>-5.146864766136064</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3504015243892618</v>
+      </c>
+      <c r="T77">
+        <v>3.46206940506481</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04671915643252897</v>
+      </c>
+      <c r="W77">
+        <v>0.2276434654439121</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1730339127130702</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2603329801802495</v>
+      </c>
+      <c r="C78">
+        <v>-16.13605879384835</v>
+      </c>
+      <c r="D78">
+        <v>17.25572831722765</v>
+      </c>
+      <c r="E78">
+        <v>43.04469880702864</v>
+      </c>
+      <c r="F78">
+        <v>44.191787111076</v>
+      </c>
+      <c r="G78">
+        <v>10.8</v>
+      </c>
+      <c r="H78">
+        <v>57</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.942</v>
+      </c>
+      <c r="K78">
+        <v>1.14</v>
+      </c>
+      <c r="L78">
+        <v>1.802</v>
+      </c>
+      <c r="M78">
+        <v>10.55299876212495</v>
+      </c>
+      <c r="N78">
+        <v>-8.750998762124949</v>
+      </c>
+      <c r="O78">
+        <v>-2.362769665773736</v>
+      </c>
+      <c r="P78">
+        <v>-6.388229096351212</v>
+      </c>
+      <c r="Q78">
+        <v>-5.248229096351213</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3633849212388144</v>
+      </c>
+      <c r="T78">
+        <v>3.606322296942511</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.04610443068999569</v>
+      </c>
+      <c r="W78">
+        <v>0.227790261951229</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1707571507036877</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2623329801802495</v>
+      </c>
+      <c r="C79">
+        <v>-16.87192057082593</v>
+      </c>
+      <c r="D79">
+        <v>17.10133742329054</v>
+      </c>
+      <c r="E79">
+        <v>43.62616969006911</v>
+      </c>
+      <c r="F79">
+        <v>44.77325799411647</v>
+      </c>
+      <c r="G79">
+        <v>10.8</v>
+      </c>
+      <c r="H79">
+        <v>57</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.942</v>
+      </c>
+      <c r="K79">
+        <v>1.14</v>
+      </c>
+      <c r="L79">
+        <v>1.802</v>
+      </c>
+      <c r="M79">
+        <v>10.69185400899501</v>
+      </c>
+      <c r="N79">
+        <v>-8.889854008995014</v>
+      </c>
+      <c r="O79">
+        <v>-2.400260582428654</v>
+      </c>
+      <c r="P79">
+        <v>-6.48959342656636</v>
+      </c>
+      <c r="Q79">
+        <v>-5.34959342656636</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3774973091187628</v>
+      </c>
+      <c r="T79">
+        <v>3.763118918548707</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04550567184986588</v>
+      </c>
+      <c r="W79">
+        <v>0.227933245562252</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1685395253698736</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2643329801802495</v>
+      </c>
+      <c r="C80">
+        <v>-17.60504410714685</v>
+      </c>
+      <c r="D80">
+        <v>16.94968477001009</v>
+      </c>
+      <c r="E80">
+        <v>44.20764057310959</v>
+      </c>
+      <c r="F80">
+        <v>45.35472887715694</v>
+      </c>
+      <c r="G80">
+        <v>10.8</v>
+      </c>
+      <c r="H80">
+        <v>57</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.942</v>
+      </c>
+      <c r="K80">
+        <v>1.14</v>
+      </c>
+      <c r="L80">
+        <v>1.802</v>
+      </c>
+      <c r="M80">
+        <v>10.83070925586508</v>
+      </c>
+      <c r="N80">
+        <v>-9.028709255865079</v>
+      </c>
+      <c r="O80">
+        <v>-2.437751499083572</v>
+      </c>
+      <c r="P80">
+        <v>-6.590957756781508</v>
+      </c>
+      <c r="Q80">
+        <v>-5.450957756781508</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3928926413514338</v>
+      </c>
+      <c r="T80">
+        <v>3.934169778482739</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04492226580050861</v>
+      </c>
+      <c r="W80">
+        <v>0.2280725629268386</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.166378762224106</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2663329801802495</v>
+      </c>
+      <c r="C81">
+        <v>-18.33550160967943</v>
+      </c>
+      <c r="D81">
+        <v>16.80069815051798</v>
+      </c>
+      <c r="E81">
+        <v>44.78911145615006</v>
+      </c>
+      <c r="F81">
+        <v>45.93619976019742</v>
+      </c>
+      <c r="G81">
+        <v>10.8</v>
+      </c>
+      <c r="H81">
+        <v>57</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.942</v>
+      </c>
+      <c r="K81">
+        <v>1.14</v>
+      </c>
+      <c r="L81">
+        <v>1.802</v>
+      </c>
+      <c r="M81">
+        <v>10.96956450273514</v>
+      </c>
+      <c r="N81">
+        <v>-9.167564502735145</v>
+      </c>
+      <c r="O81">
+        <v>-2.475242415738489</v>
+      </c>
+      <c r="P81">
+        <v>-6.692322086996656</v>
+      </c>
+      <c r="Q81">
+        <v>-5.552322086996656</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4097541957015022</v>
+      </c>
+      <c r="T81">
+        <v>4.121511196505728</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04435362952455281</v>
+      </c>
+      <c r="W81">
+        <v>0.2282083532695368</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1642727019427882</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2683329801802495</v>
+      </c>
+      <c r="C82">
+        <v>-19.06336276863864</v>
+      </c>
+      <c r="D82">
+        <v>16.65430787459925</v>
+      </c>
+      <c r="E82">
+        <v>45.37058233919053</v>
+      </c>
+      <c r="F82">
+        <v>46.51767064323789</v>
+      </c>
+      <c r="G82">
+        <v>10.8</v>
+      </c>
+      <c r="H82">
+        <v>57</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.942</v>
+      </c>
+      <c r="K82">
+        <v>1.14</v>
+      </c>
+      <c r="L82">
+        <v>1.802</v>
+      </c>
+      <c r="M82">
+        <v>11.10841974960521</v>
+      </c>
+      <c r="N82">
+        <v>-9.30641974960521</v>
+      </c>
+      <c r="O82">
+        <v>-2.512733332393407</v>
+      </c>
+      <c r="P82">
+        <v>-6.793686417211803</v>
+      </c>
+      <c r="Q82">
+        <v>-5.653686417211803</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4283019054865773</v>
+      </c>
+      <c r="T82">
+        <v>4.327586756331014</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04379920915549591</v>
+      </c>
+      <c r="W82">
+        <v>0.2283407488536676</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1622192931685034</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2703329801802495</v>
+      </c>
+      <c r="C83">
+        <v>-19.78869486628131</v>
+      </c>
+      <c r="D83">
+        <v>16.51044665999705</v>
+      </c>
+      <c r="E83">
+        <v>45.95205322223101</v>
+      </c>
+      <c r="F83">
+        <v>47.09914152627837</v>
+      </c>
+      <c r="G83">
+        <v>10.8</v>
+      </c>
+      <c r="H83">
+        <v>57</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.942</v>
+      </c>
+      <c r="K83">
+        <v>1.14</v>
+      </c>
+      <c r="L83">
+        <v>1.802</v>
+      </c>
+      <c r="M83">
+        <v>11.24727499647527</v>
+      </c>
+      <c r="N83">
+        <v>-9.445274996475275</v>
+      </c>
+      <c r="O83">
+        <v>-2.550224249048324</v>
+      </c>
+      <c r="P83">
+        <v>-6.895050747426951</v>
+      </c>
+      <c r="Q83">
+        <v>-5.755050747426951</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4488020057753446</v>
+      </c>
+      <c r="T83">
+        <v>4.555354480348436</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04325847817826756</v>
+      </c>
+      <c r="W83">
+        <v>0.2284698754110297</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1602165858454354</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2723329801802495</v>
+      </c>
+      <c r="C84">
+        <v>-20.51156288001616</v>
+      </c>
+      <c r="D84">
+        <v>16.36904952930267</v>
+      </c>
+      <c r="E84">
+        <v>46.53352410527148</v>
+      </c>
+      <c r="F84">
+        <v>47.68061240931884</v>
+      </c>
+      <c r="G84">
+        <v>10.8</v>
+      </c>
+      <c r="H84">
+        <v>57</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.942</v>
+      </c>
+      <c r="K84">
+        <v>1.14</v>
+      </c>
+      <c r="L84">
+        <v>1.802</v>
+      </c>
+      <c r="M84">
+        <v>11.38613024334534</v>
+      </c>
+      <c r="N84">
+        <v>-9.58413024334534</v>
+      </c>
+      <c r="O84">
+        <v>-2.587715165703242</v>
+      </c>
+      <c r="P84">
+        <v>-6.996415077642098</v>
+      </c>
+      <c r="Q84">
+        <v>-5.856415077642098</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.471579894985086</v>
+      </c>
+      <c r="T84">
+        <v>4.808429729256683</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04273093576145941</v>
+      </c>
+      <c r="W84">
+        <v>0.2285958525401635</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1582627250424422</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2743329801802495</v>
+      </c>
+      <c r="C85">
+        <v>-21.23202958026047</v>
+      </c>
+      <c r="D85">
+        <v>16.23005371209885</v>
+      </c>
+      <c r="E85">
+        <v>47.11499498831196</v>
+      </c>
+      <c r="F85">
+        <v>48.26208329235931</v>
+      </c>
+      <c r="G85">
+        <v>10.8</v>
+      </c>
+      <c r="H85">
+        <v>57</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.942</v>
+      </c>
+      <c r="K85">
+        <v>1.14</v>
+      </c>
+      <c r="L85">
+        <v>1.802</v>
+      </c>
+      <c r="M85">
+        <v>11.52498549021541</v>
+      </c>
+      <c r="N85">
+        <v>-9.722985490215406</v>
+      </c>
+      <c r="O85">
+        <v>-2.62520608235816</v>
+      </c>
+      <c r="P85">
+        <v>-7.097779407857246</v>
+      </c>
+      <c r="Q85">
+        <v>-5.957779407857246</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4970375358665616</v>
+      </c>
+      <c r="T85">
+        <v>5.091278536860017</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.04221610521011653</v>
+      </c>
+      <c r="W85">
+        <v>0.2287187940758242</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1563559452226538</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2763329801802495</v>
+      </c>
+      <c r="C86">
+        <v>-21.95015562335308</v>
+      </c>
+      <c r="D86">
+        <v>16.0933985520467</v>
+      </c>
+      <c r="E86">
+        <v>47.69646587135242</v>
+      </c>
+      <c r="F86">
+        <v>48.84355417539978</v>
+      </c>
+      <c r="G86">
+        <v>10.8</v>
+      </c>
+      <c r="H86">
+        <v>57</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.942</v>
+      </c>
+      <c r="K86">
+        <v>1.14</v>
+      </c>
+      <c r="L86">
+        <v>1.802</v>
+      </c>
+      <c r="M86">
+        <v>11.66384073708547</v>
+      </c>
+      <c r="N86">
+        <v>-9.861840737085469</v>
+      </c>
+      <c r="O86">
+        <v>-2.662696999013077</v>
+      </c>
+      <c r="P86">
+        <v>-7.199143738072392</v>
+      </c>
+      <c r="Q86">
+        <v>-6.059143738072392</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5256773818582214</v>
+      </c>
+      <c r="T86">
+        <v>5.409483445413765</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.04171353252904372</v>
+      </c>
+      <c r="W86">
+        <v>0.2288388084320644</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1544945649223841</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2783329801802495</v>
+      </c>
+      <c r="C87">
+        <v>-22.6659996398129</v>
+      </c>
+      <c r="D87">
+        <v>15.95902541862735</v>
+      </c>
+      <c r="E87">
+        <v>48.2779367543929</v>
+      </c>
+      <c r="F87">
+        <v>49.42502505844026</v>
+      </c>
+      <c r="G87">
+        <v>10.8</v>
+      </c>
+      <c r="H87">
+        <v>57</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.942</v>
+      </c>
+      <c r="K87">
+        <v>1.14</v>
+      </c>
+      <c r="L87">
+        <v>1.802</v>
+      </c>
+      <c r="M87">
+        <v>11.80269598395553</v>
+      </c>
+      <c r="N87">
+        <v>-10.00069598395553</v>
+      </c>
+      <c r="O87">
+        <v>-2.700187915667994</v>
+      </c>
+      <c r="P87">
+        <v>-7.30050806828754</v>
+      </c>
+      <c r="Q87">
+        <v>-6.16050806828754</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.558135873982103</v>
+      </c>
+      <c r="T87">
+        <v>5.770115675108017</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04122278508752555</v>
+      </c>
+      <c r="W87">
+        <v>0.2289559989210989</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1526769818056501</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2803329801802495</v>
+      </c>
+      <c r="C88">
+        <v>-23.37961831821215</v>
+      </c>
+      <c r="D88">
+        <v>15.82687762326858</v>
+      </c>
+      <c r="E88">
+        <v>48.85940763743337</v>
+      </c>
+      <c r="F88">
+        <v>50.00649594148073</v>
+      </c>
+      <c r="G88">
+        <v>10.8</v>
+      </c>
+      <c r="H88">
+        <v>57</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.942</v>
+      </c>
+      <c r="K88">
+        <v>1.14</v>
+      </c>
+      <c r="L88">
+        <v>1.802</v>
+      </c>
+      <c r="M88">
+        <v>11.9415512308256</v>
+      </c>
+      <c r="N88">
+        <v>-10.1395512308256</v>
+      </c>
+      <c r="O88">
+        <v>-2.737678832322912</v>
+      </c>
+      <c r="P88">
+        <v>-7.401872398502688</v>
+      </c>
+      <c r="Q88">
+        <v>-6.261872398502688</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.595231293552253</v>
+      </c>
+      <c r="T88">
+        <v>6.182266794758589</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.0407434503772055</v>
+      </c>
+      <c r="W88">
+        <v>0.2290704640499233</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1509016680637241</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2823329801802495</v>
+      </c>
+      <c r="C89">
+        <v>-24.09106648491708</v>
+      </c>
+      <c r="D89">
+        <v>15.69690033960412</v>
+      </c>
+      <c r="E89">
+        <v>49.44087852047385</v>
+      </c>
+      <c r="F89">
+        <v>50.5879668245212</v>
+      </c>
+      <c r="G89">
+        <v>10.8</v>
+      </c>
+      <c r="H89">
+        <v>57</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.942</v>
+      </c>
+      <c r="K89">
+        <v>1.14</v>
+      </c>
+      <c r="L89">
+        <v>1.802</v>
+      </c>
+      <c r="M89">
+        <v>12.08040647769566</v>
+      </c>
+      <c r="N89">
+        <v>-10.27840647769566</v>
+      </c>
+      <c r="O89">
+        <v>-2.77516974897783</v>
+      </c>
+      <c r="P89">
+        <v>-7.503236728717836</v>
+      </c>
+      <c r="Q89">
+        <v>-6.363236728717836</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6380337007485803</v>
+      </c>
+      <c r="T89">
+        <v>6.657825778970789</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04027513485562842</v>
+      </c>
+      <c r="W89">
+        <v>0.2291822977964759</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1491671661319571</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2843329801802496</v>
+      </c>
+      <c r="C90">
+        <v>-24.80039717993133</v>
+      </c>
+      <c r="D90">
+        <v>15.56904052763035</v>
+      </c>
+      <c r="E90">
+        <v>50.02234940351432</v>
+      </c>
+      <c r="F90">
+        <v>51.16943770756168</v>
+      </c>
+      <c r="G90">
+        <v>10.8</v>
+      </c>
+      <c r="H90">
+        <v>57</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.942</v>
+      </c>
+      <c r="K90">
+        <v>1.14</v>
+      </c>
+      <c r="L90">
+        <v>1.802</v>
+      </c>
+      <c r="M90">
+        <v>12.21926172456573</v>
+      </c>
+      <c r="N90">
+        <v>-10.41726172456573</v>
+      </c>
+      <c r="O90">
+        <v>-2.812660665632747</v>
+      </c>
+      <c r="P90">
+        <v>-7.604601058932983</v>
+      </c>
+      <c r="Q90">
+        <v>-6.464601058932983</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6879698424776288</v>
+      </c>
+      <c r="T90">
+        <v>7.212644593885022</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03981746286863264</v>
+      </c>
+      <c r="W90">
+        <v>0.2292915898669705</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1474720846986394</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2863329801802495</v>
+      </c>
+      <c r="C91">
+        <v>-25.50766172906262</v>
+      </c>
+      <c r="D91">
+        <v>15.44324686153953</v>
+      </c>
+      <c r="E91">
+        <v>50.60382028655479</v>
+      </c>
+      <c r="F91">
+        <v>51.75090859060215</v>
+      </c>
+      <c r="G91">
+        <v>10.8</v>
+      </c>
+      <c r="H91">
+        <v>57</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.942</v>
+      </c>
+      <c r="K91">
+        <v>1.14</v>
+      </c>
+      <c r="L91">
+        <v>1.802</v>
+      </c>
+      <c r="M91">
+        <v>12.35811697143579</v>
+      </c>
+      <c r="N91">
+        <v>-10.5561169714358</v>
+      </c>
+      <c r="O91">
+        <v>-2.850151582287665</v>
+      </c>
+      <c r="P91">
+        <v>-7.70596538914813</v>
+      </c>
+      <c r="Q91">
+        <v>-6.56596538914813</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7469852827028676</v>
+      </c>
+      <c r="T91">
+        <v>7.868339556965478</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03937007564538958</v>
+      </c>
+      <c r="W91">
+        <v>0.229398425935881</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1458150949829243</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2883329801802496</v>
+      </c>
+      <c r="C92">
+        <v>-26.21290981261891</v>
+      </c>
+      <c r="D92">
+        <v>15.31946966102371</v>
+      </c>
+      <c r="E92">
+        <v>51.18529116959527</v>
+      </c>
+      <c r="F92">
+        <v>52.33237947364263</v>
+      </c>
+      <c r="G92">
+        <v>10.8</v>
+      </c>
+      <c r="H92">
+        <v>57</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.942</v>
+      </c>
+      <c r="K92">
+        <v>1.14</v>
+      </c>
+      <c r="L92">
+        <v>1.802</v>
+      </c>
+      <c r="M92">
+        <v>12.49697221830586</v>
+      </c>
+      <c r="N92">
+        <v>-10.69497221830586</v>
+      </c>
+      <c r="O92">
+        <v>-2.887642498942582</v>
+      </c>
+      <c r="P92">
+        <v>-7.807329719363278</v>
+      </c>
+      <c r="Q92">
+        <v>-6.667329719363278</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8178038109731547</v>
+      </c>
+      <c r="T92">
+        <v>8.655173512662028</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0389326303604408</v>
+      </c>
+      <c r="W92">
+        <v>0.2295028878699268</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1441949272608919</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2903329801802495</v>
+      </c>
+      <c r="C93">
+        <v>-26.91618953082721</v>
+      </c>
+      <c r="D93">
+        <v>15.19766082585589</v>
+      </c>
+      <c r="E93">
+        <v>51.76676205263574</v>
+      </c>
+      <c r="F93">
+        <v>52.9138503566831</v>
+      </c>
+      <c r="G93">
+        <v>10.8</v>
+      </c>
+      <c r="H93">
+        <v>57</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.942</v>
+      </c>
+      <c r="K93">
+        <v>1.14</v>
+      </c>
+      <c r="L93">
+        <v>1.802</v>
+      </c>
+      <c r="M93">
+        <v>12.63582746517593</v>
+      </c>
+      <c r="N93">
+        <v>-10.83382746517593</v>
+      </c>
+      <c r="O93">
+        <v>-2.9251334155975</v>
+      </c>
+      <c r="P93">
+        <v>-7.908694049578425</v>
+      </c>
+      <c r="Q93">
+        <v>-6.768694049578426</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9043597899701719</v>
+      </c>
+      <c r="T93">
+        <v>9.616859458513366</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03850479925757882</v>
+      </c>
+      <c r="W93">
+        <v>0.2296050539372902</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1426103676206623</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2923329801802496</v>
+      </c>
+      <c r="C94">
+        <v>-27.61754746615612</v>
+      </c>
+      <c r="D94">
+        <v>15.07777377356745</v>
+      </c>
+      <c r="E94">
+        <v>52.34823293567622</v>
+      </c>
+      <c r="F94">
+        <v>53.49532123972357</v>
+      </c>
+      <c r="G94">
+        <v>10.8</v>
+      </c>
+      <c r="H94">
+        <v>57</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.942</v>
+      </c>
+      <c r="K94">
+        <v>1.14</v>
+      </c>
+      <c r="L94">
+        <v>1.802</v>
+      </c>
+      <c r="M94">
+        <v>12.77468271204599</v>
+      </c>
+      <c r="N94">
+        <v>-10.97268271204599</v>
+      </c>
+      <c r="O94">
+        <v>-2.962624332252418</v>
+      </c>
+      <c r="P94">
+        <v>-8.010058379793573</v>
+      </c>
+      <c r="Q94">
+        <v>-6.870058379793574</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.012554763716444</v>
+      </c>
+      <c r="T94">
+        <v>10.81896689082754</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.038086268830866</v>
+      </c>
+      <c r="W94">
+        <v>0.2297049990031892</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1410602549291333</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2943329801802495</v>
+      </c>
+      <c r="C95">
+        <v>-28.3170287427116</v>
+      </c>
+      <c r="D95">
+        <v>14.95976338005245</v>
+      </c>
+      <c r="E95">
+        <v>52.92970381871669</v>
+      </c>
+      <c r="F95">
+        <v>54.07679212276405</v>
+      </c>
+      <c r="G95">
+        <v>10.8</v>
+      </c>
+      <c r="H95">
+        <v>57</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.942</v>
+      </c>
+      <c r="K95">
+        <v>1.14</v>
+      </c>
+      <c r="L95">
+        <v>1.802</v>
+      </c>
+      <c r="M95">
+        <v>12.91353795891606</v>
+      </c>
+      <c r="N95">
+        <v>-11.11153795891606</v>
+      </c>
+      <c r="O95">
+        <v>-3.000115248907335</v>
+      </c>
+      <c r="P95">
+        <v>-8.111422710008721</v>
+      </c>
+      <c r="Q95">
+        <v>-6.971422710008722</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.151662587104507</v>
+      </c>
+      <c r="T95">
+        <v>12.36453358951719</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.0376767390584911</v>
+      </c>
+      <c r="W95">
+        <v>0.2298027947128323</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1395434779944115</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2963329801802496</v>
+      </c>
+      <c r="C96">
+        <v>-29.0146770828652</v>
+      </c>
+      <c r="D96">
+        <v>14.84358592293932</v>
+      </c>
+      <c r="E96">
+        <v>53.51117470175716</v>
+      </c>
+      <c r="F96">
+        <v>54.65826300580452</v>
+      </c>
+      <c r="G96">
+        <v>10.8</v>
+      </c>
+      <c r="H96">
+        <v>57</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.942</v>
+      </c>
+      <c r="K96">
+        <v>1.14</v>
+      </c>
+      <c r="L96">
+        <v>1.802</v>
+      </c>
+      <c r="M96">
+        <v>13.05239320578612</v>
+      </c>
+      <c r="N96">
+        <v>-11.25039320578612</v>
+      </c>
+      <c r="O96">
+        <v>-3.037606165562253</v>
+      </c>
+      <c r="P96">
+        <v>-8.212787040223869</v>
+      </c>
+      <c r="Q96">
+        <v>-7.07278704022387</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.337139684955259</v>
+      </c>
+      <c r="T96">
+        <v>14.42528918777006</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.03727592268552843</v>
+      </c>
+      <c r="W96">
+        <v>0.2298985096626958</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1380589729093645</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2983329801802496</v>
+      </c>
+      <c r="C97">
+        <v>-29.71053486126387</v>
+      </c>
+      <c r="D97">
+        <v>14.72919902758113</v>
+      </c>
+      <c r="E97">
+        <v>54.09264558479764</v>
+      </c>
+      <c r="F97">
+        <v>55.239733888845</v>
+      </c>
+      <c r="G97">
+        <v>10.8</v>
+      </c>
+      <c r="H97">
+        <v>57</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.942</v>
+      </c>
+      <c r="K97">
+        <v>1.14</v>
+      </c>
+      <c r="L97">
+        <v>1.802</v>
+      </c>
+      <c r="M97">
+        <v>13.19124845265619</v>
+      </c>
+      <c r="N97">
+        <v>-11.38924845265619</v>
+      </c>
+      <c r="O97">
+        <v>-3.07509708221717</v>
+      </c>
+      <c r="P97">
+        <v>-8.314151370439017</v>
+      </c>
+      <c r="Q97">
+        <v>-7.174151370439017</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.596807621946311</v>
+      </c>
+      <c r="T97">
+        <v>17.31034702532408</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03688354455199655</v>
+      </c>
+      <c r="W97">
+        <v>0.2299922095609832</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1366057205629502</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3003329801802495</v>
+      </c>
+      <c r="C98">
+        <v>-30.40464315636173</v>
+      </c>
+      <c r="D98">
+        <v>14.61656161552373</v>
+      </c>
+      <c r="E98">
+        <v>54.6741164678381</v>
+      </c>
+      <c r="F98">
+        <v>55.82120477188546</v>
+      </c>
+      <c r="G98">
+        <v>10.8</v>
+      </c>
+      <c r="H98">
+        <v>57</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.942</v>
+      </c>
+      <c r="K98">
+        <v>1.14</v>
+      </c>
+      <c r="L98">
+        <v>1.802</v>
+      </c>
+      <c r="M98">
+        <v>13.33010369952625</v>
+      </c>
+      <c r="N98">
+        <v>-11.52810369952625</v>
+      </c>
+      <c r="O98">
+        <v>-3.112587998872088</v>
+      </c>
+      <c r="P98">
+        <v>-8.415515700654161</v>
+      </c>
+      <c r="Q98">
+        <v>-7.275515700654162</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.986309527432884</v>
+      </c>
+      <c r="T98">
+        <v>21.63793378165505</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03649934096291325</v>
+      </c>
+      <c r="W98">
+        <v>0.2300839573780563</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1351827443070861</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3023329801802496</v>
+      </c>
+      <c r="C99">
+        <v>-31.09704179960532</v>
+      </c>
+      <c r="D99">
+        <v>14.50563385532061</v>
+      </c>
+      <c r="E99">
+        <v>55.25558735087858</v>
+      </c>
+      <c r="F99">
+        <v>56.40267565492594</v>
+      </c>
+      <c r="G99">
+        <v>10.8</v>
+      </c>
+      <c r="H99">
+        <v>57</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.942</v>
+      </c>
+      <c r="K99">
+        <v>1.14</v>
+      </c>
+      <c r="L99">
+        <v>1.802</v>
+      </c>
+      <c r="M99">
+        <v>13.46895894639631</v>
+      </c>
+      <c r="N99">
+        <v>-11.66695894639632</v>
+      </c>
+      <c r="O99">
+        <v>-3.150078915527005</v>
+      </c>
+      <c r="P99">
+        <v>-8.516880030869309</v>
+      </c>
+      <c r="Q99">
+        <v>-7.37688003086931</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.635479369910513</v>
+      </c>
+      <c r="T99">
+        <v>28.85057837554006</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03612305909731621</v>
+      </c>
+      <c r="W99">
+        <v>0.2301738134875609</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1337891077678378</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3043329801802495</v>
+      </c>
+      <c r="C100">
+        <v>-31.78776942239596</v>
+      </c>
+      <c r="D100">
+        <v>14.39637711557044</v>
+      </c>
+      <c r="E100">
+        <v>55.83705823391905</v>
+      </c>
+      <c r="F100">
+        <v>56.98414653796641</v>
+      </c>
+      <c r="G100">
+        <v>10.8</v>
+      </c>
+      <c r="H100">
+        <v>57</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.942</v>
+      </c>
+      <c r="K100">
+        <v>1.14</v>
+      </c>
+      <c r="L100">
+        <v>1.802</v>
+      </c>
+      <c r="M100">
+        <v>13.60781419326638</v>
+      </c>
+      <c r="N100">
+        <v>-11.80581419326638</v>
+      </c>
+      <c r="O100">
+        <v>-3.187569832181923</v>
+      </c>
+      <c r="P100">
+        <v>-8.618244361084457</v>
+      </c>
+      <c r="Q100">
+        <v>-7.478244361084458</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.933819054865769</v>
+      </c>
+      <c r="T100">
+        <v>43.27586756331009</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03575445645346605</v>
+      </c>
+      <c r="W100">
+        <v>0.2302618357989123</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1324239127906149</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3063329801802496</v>
+      </c>
+      <c r="C101">
+        <v>-32.4768635009458</v>
+      </c>
+      <c r="D101">
+        <v>14.28875392006108</v>
+      </c>
+      <c r="E101">
+        <v>56.41852911695953</v>
+      </c>
+      <c r="F101">
+        <v>57.56561742100688</v>
+      </c>
+      <c r="G101">
+        <v>10.8</v>
+      </c>
+      <c r="H101">
+        <v>57</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.942</v>
+      </c>
+      <c r="K101">
+        <v>1.14</v>
+      </c>
+      <c r="L101">
+        <v>1.802</v>
+      </c>
+      <c r="M101">
+        <v>13.74666944013645</v>
+      </c>
+      <c r="N101">
+        <v>-11.94466944013645</v>
+      </c>
+      <c r="O101">
+        <v>-3.225060748836841</v>
+      </c>
+      <c r="P101">
+        <v>-8.719608691299605</v>
+      </c>
+      <c r="Q101">
+        <v>-7.579608691299605</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.828838109731538</v>
+      </c>
+      <c r="T101">
+        <v>86.55173512662019</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03539330032767346</v>
+      </c>
+      <c r="W101">
+        <v>0.2303480798817516</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1310862975099016</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
